--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1666">
   <si>
     <t>Measure</t>
   </si>
@@ -951,6 +951,9 @@
     <t>dlp/2026/pixar-cars-wall-e-june</t>
   </si>
   <si>
+    <t>dlp/2026/pride-2026</t>
+  </si>
+  <si>
     <t>dlp/2026/raiponce-tangled-spin-june</t>
   </si>
   <si>
@@ -975,6 +978,9 @@
     <t>dlp/2025/disneyland-hotel-oe-2025-01</t>
   </si>
   <si>
+    <t>dlp/2025/goofy-le-2025-07</t>
+  </si>
+  <si>
     <t>dlp/2025/halloween-2025-le-2025-09-20</t>
   </si>
   <si>
@@ -1050,9 +1056,6 @@
     <t>dlp/2025/genie-2026-2025-12-06</t>
   </si>
   <si>
-    <t>dlp/2025/goofy-le-2025-07</t>
-  </si>
-  <si>
     <t>dlp/2025/goofy-max-powerline-le-2025-12-06</t>
   </si>
   <si>
@@ -1188,9 +1191,6 @@
     <t>dlp/2026/pin-trading-25th-anniversary-mickey</t>
   </si>
   <si>
-    <t>dlp/2026/pride-2026</t>
-  </si>
-  <si>
     <t>dlp/2026/princess-studio-ariel</t>
   </si>
   <si>
@@ -1758,6 +1758,9 @@
     <t>Pixar pins (Cars, WALL-E)</t>
   </si>
   <si>
+    <t>Pride - Mickey and Minnie rainbow</t>
+  </si>
+  <si>
     <t>Tangled LE pins (June 6)</t>
   </si>
   <si>
@@ -1782,6 +1785,9 @@
     <t>Disneyland Hotel open edition pins</t>
   </si>
   <si>
+    <t>Goofy limited edition pin (July)</t>
+  </si>
+  <si>
     <t>Halloween 2025 limited edition pins</t>
   </si>
   <si>
@@ -1857,9 +1863,6 @@
     <t>Genie 2026-themed pin</t>
   </si>
   <si>
-    <t>Goofy limited edition pin (July)</t>
-  </si>
-  <si>
     <t>Goofy, Max and Powerline limited edition pin</t>
   </si>
   <si>
@@ -1995,9 +1998,6 @@
     <t>Pin Trading 25th anniversary classic Mickey</t>
   </si>
   <si>
-    <t>Pride - Mickey and Minnie rainbow</t>
-  </si>
-  <si>
     <t>Princess Studio - Ariel</t>
   </si>
   <si>
@@ -2538,6 +2538,9 @@
     <t>2026-03-14</t>
   </si>
   <si>
+    <t>2026-06-27</t>
+  </si>
+  <si>
     <t>2026-04-11</t>
   </si>
   <si>
@@ -3717,6 +3720,9 @@
     <t>Lightning McQueen – Pixar pins (Cars, WALL-E) | Mater – Pixar pins (Cars, WALL-E) | EVE; WALL-E</t>
   </si>
   <si>
+    <t>Mickey Mouse – Pride - Mickey and Minnie rainbow | Mickey Mouse; Minnie Mouse | Minnie Mouse – Pride - Mickey and Minnie rainbow</t>
+  </si>
+  <si>
     <t>Maximus; Pascal | Flynn Rider; Rapunzel | The Lover; The Satyr; Vladimir</t>
   </si>
   <si>
@@ -3741,6 +3747,9 @@
     <t>Mickey Mouse; Minnie Mouse | Mickey Mouse – Disneyland Hotel open edition pins</t>
   </si>
   <si>
+    <t>Goofy; Rafiki | Rafiki – Goofy limited edition pin (July)</t>
+  </si>
+  <si>
     <t>Halloween Mickey &amp; Minnie Hot Air Balloon | Halloween Mickey Framed</t>
   </si>
   <si>
@@ -3816,9 +3825,6 @@
     <t>Genie – Genie 2026-themed pin</t>
   </si>
   <si>
-    <t>Goofy; Rafiki</t>
-  </si>
-  <si>
     <t>Goofy; Max; Powerline</t>
   </si>
   <si>
@@ -4008,6 +4014,9 @@
     <t>Tarzan – Tarzan</t>
   </si>
   <si>
+    <t>Forky; Karen Beverly</t>
+  </si>
+  <si>
     <t>Hercules – Voyage Series - Hercules</t>
   </si>
   <si>
@@ -4656,6 +4665,9 @@
     <t>dlp/2026/pixar-cars-wall-e-june/lightning-mcqueen | dlp/2026/pixar-cars-wall-e-june/mater | dlp/2026/pixar-cars-wall-e-june/wall-e-and-eve</t>
   </si>
   <si>
+    <t>dlp/2026/pride-2026/mickey | dlp/2026/pride-2026/mickey-and-minnie | dlp/2026/pride-2026/minnie</t>
+  </si>
+  <si>
     <t>dlp/2026/raiponce-tangled-spin-june/maximus-and-pascal | dlp/2026/raiponce-tangled-spin-june/rapunzel-and-flynn | dlp/2026/raiponce-tangled-spin-june/satyr-vladimir-lover</t>
   </si>
   <si>
@@ -4680,6 +4692,9 @@
     <t>dlp/2025/disneyland-hotel-oe-2025-01/mickey-and-minnie-royal-banquet | dlp/2025/disneyland-hotel-oe-2025-01/mickey-clock</t>
   </si>
   <si>
+    <t>dlp/2025/goofy-le-2025-07/goofy | dlp/2025/goofy-le-2025-07/rafiki</t>
+  </si>
+  <si>
     <t>dlp/2025/halloween-2025-le-2025-09-20/mickey-and-minnie-hot-air-balloon | dlp/2025/halloween-2025-le-2025-09-20/mickey-framed</t>
   </si>
   <si>
@@ -4758,9 +4773,6 @@
     <t>dlp/2025/genie-2026-2025-12-06/genie</t>
   </si>
   <si>
-    <t>dlp/2025/goofy-le-2025-07/goofy</t>
-  </si>
-  <si>
     <t>dlp/2025/goofy-max-powerline-le-2025-12-06/goofy-max-powerline</t>
   </si>
   <si>
@@ -4896,9 +4908,6 @@
     <t>dlp/2026/pin-trading-25th-anniversary-mickey/mickey</t>
   </si>
   <si>
-    <t>dlp/2026/pride-2026/mickey-and-minnie</t>
-  </si>
-  <si>
     <t>dlp/2026/princess-studio-ariel/ariel</t>
   </si>
   <si>
@@ -4960,6 +4969,9 @@
   </si>
   <si>
     <t>dlp/2026/tarzan/tarzan</t>
+  </si>
+  <si>
+    <t>dlp/2026/toy-story-5-open-edition/karen-and-forky</t>
   </si>
   <si>
     <t>dlp/2026/voyage-series-hercules/hercules</t>
@@ -5362,7 +5374,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5370,7 +5382,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>745</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5378,7 +5390,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6498,7 +6510,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R344"/>
+  <dimension ref="A1:R345"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -6680,13 +6692,13 @@
         <v>84</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="N4" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -6724,13 +6736,13 @@
         <v>84</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M5" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N5" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -6932,13 +6944,13 @@
         <v>84</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M10" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="N10" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -6973,13 +6985,13 @@
         <v>84</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M11" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="N11" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7017,13 +7029,13 @@
         <v>84</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M12" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N12" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7102,13 +7114,13 @@
         <v>84</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M14" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="N14" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7146,13 +7158,13 @@
         <v>84</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M15" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N15" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7190,13 +7202,13 @@
         <v>84</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M16" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N16" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -7401,13 +7413,13 @@
         <v>84</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M21" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="N21" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -7445,13 +7457,13 @@
         <v>84</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M22" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N22" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -7486,13 +7498,13 @@
         <v>84</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M23" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="N23" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -7527,13 +7539,13 @@
         <v>84</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M24" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="N24" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -7568,13 +7580,13 @@
         <v>84</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M25" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="N25" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -7609,13 +7621,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M26" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N26" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -7650,13 +7662,13 @@
         <v>84</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M27" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="N27" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -7691,13 +7703,13 @@
         <v>84</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M28" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="N28" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -7732,13 +7744,13 @@
         <v>84</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M29" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="N29" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -7776,13 +7788,13 @@
         <v>84</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M30" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="N30" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -7817,13 +7829,13 @@
         <v>84</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M31" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N31" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -7858,13 +7870,13 @@
         <v>84</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M32" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N32" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -7899,13 +7911,13 @@
         <v>84</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="M33" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N33" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -7940,13 +7952,13 @@
         <v>84</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M34" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="N34" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -7981,13 +7993,13 @@
         <v>84</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M35" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="N35" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -8535,13 +8547,13 @@
         <v>84</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="M48" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N48" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -8579,13 +8591,13 @@
         <v>84</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M49" t="s">
         <v>440</v>
       </c>
       <c r="N49" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -8623,13 +8635,13 @@
         <v>84</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M50" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N50" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -8667,13 +8679,13 @@
         <v>84</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M51" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N51" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -8711,13 +8723,13 @@
         <v>84</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M52" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="N52" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -8752,13 +8764,13 @@
         <v>84</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M53" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="N53" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -8793,13 +8805,13 @@
         <v>84</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="M54" t="s">
         <v>445</v>
       </c>
       <c r="N54" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -8834,13 +8846,13 @@
         <v>84</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M55" t="s">
         <v>446</v>
       </c>
       <c r="N55" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -8878,13 +8890,13 @@
         <v>84</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M56" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="N56" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -8919,13 +8931,13 @@
         <v>84</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M57" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N57" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -8960,13 +8972,13 @@
         <v>84</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="M58" t="s">
         <v>448</v>
       </c>
       <c r="N58" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -9001,13 +9013,13 @@
         <v>84</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M59" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N59" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -9042,13 +9054,13 @@
         <v>84</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M60" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N60" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -9083,13 +9095,13 @@
         <v>84</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M61" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N61" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -9124,13 +9136,13 @@
         <v>84</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="M62" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N62" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -9165,13 +9177,13 @@
         <v>84</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M63" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N63" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -9206,13 +9218,13 @@
         <v>84</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M64" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="N64" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -9247,13 +9259,13 @@
         <v>84</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="M65" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N65" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -9288,13 +9300,13 @@
         <v>84</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M66" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="N66" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -9329,13 +9341,13 @@
         <v>84</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M67" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N67" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -9370,13 +9382,13 @@
         <v>84</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M68" t="s">
         <v>451</v>
       </c>
       <c r="N68" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -9414,13 +9426,13 @@
         <v>84</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M69" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N69" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -9458,13 +9470,13 @@
         <v>84</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M70" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="N70" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -9502,13 +9514,13 @@
         <v>84</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M71" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N71" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -9546,13 +9558,13 @@
         <v>84</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M72" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="N72" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -9590,13 +9602,13 @@
         <v>84</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M73" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="N73" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -9634,13 +9646,13 @@
         <v>84</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M74" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="N74" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -9675,16 +9687,16 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="M75" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N75" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -9719,16 +9731,16 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M76" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N76" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -9763,16 +9775,16 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M77" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="N77" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -9807,16 +9819,16 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="M78" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="N78" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -9851,16 +9863,16 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M79" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="N79" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -9895,16 +9907,16 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M80" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N80" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -9939,16 +9951,16 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M81" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N81" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -9983,16 +9995,16 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M82" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N82" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -10027,16 +10039,16 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M83" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N83" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -10068,16 +10080,16 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M84" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="N84" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -10112,16 +10124,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M85" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="N85" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -10156,16 +10168,16 @@
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M86" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="N86" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -10200,16 +10212,16 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M87" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N87" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -10241,16 +10253,16 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M88" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="N88" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -10285,16 +10297,16 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M89" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="N89" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -10326,16 +10338,16 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M90" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="N90" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -10370,16 +10382,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M91" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N91" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -10414,16 +10426,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M92" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N92" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -10458,16 +10470,16 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M93" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="N93" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -10502,16 +10514,16 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M94" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N94" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -10546,16 +10558,16 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M95" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="N95" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -10590,16 +10602,16 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="M96" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="N96" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -10631,16 +10643,16 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M97" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="N97" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -10672,19 +10684,19 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M98" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="N98" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -10716,16 +10728,16 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M99" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N99" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -10760,16 +10772,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M100" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="N100" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -10804,16 +10816,16 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M101" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="N101" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -10848,16 +10860,16 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M102" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="N102" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -10892,16 +10904,16 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M103" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="N103" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -10936,16 +10948,16 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M104" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="N104" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -10980,16 +10992,16 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M105" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="N105" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -11024,16 +11036,16 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M106" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N106" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -11068,16 +11080,16 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M107" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="N107" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -11112,16 +11124,16 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M108" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N108" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -11156,16 +11168,16 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M109" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="N109" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -11200,16 +11212,16 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M110" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="N110" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -11244,16 +11256,16 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M111" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="N111" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -11288,16 +11300,16 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M112" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="N112" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -11332,16 +11344,16 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M113" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N113" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -11376,16 +11388,16 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M114" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="N114" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -11420,16 +11432,16 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M115" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="N115" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -11464,16 +11476,16 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M116" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N116" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -11508,16 +11520,16 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M117" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N117" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -11549,16 +11561,16 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M118" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N118" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -11590,16 +11602,16 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M119" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="N119" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11634,16 +11646,16 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M120" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="N120" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -11678,16 +11690,16 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M121" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="N121" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -11722,16 +11734,16 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M122" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="N122" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -11766,16 +11778,16 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M123" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="N123" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -11810,16 +11822,16 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M124" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="N124" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -11854,16 +11866,16 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M125" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="N125" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -11898,16 +11910,16 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="M126" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="N126" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -11942,16 +11954,16 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M127" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N127" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -11986,16 +11998,16 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M128" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N128" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -12030,16 +12042,16 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M129" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="N129" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -12071,16 +12083,16 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M130" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="N130" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -12112,16 +12124,16 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M131" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="N131" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -12153,16 +12165,16 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M132" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N132" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -12194,16 +12206,16 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M133" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="N133" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -12235,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M134" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="N134" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -12276,16 +12288,16 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M135" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="N135" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -12317,16 +12329,16 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M136" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="N136" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -12361,16 +12373,16 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M137" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="N137" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -12405,16 +12417,16 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="M138" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="N138" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -12446,16 +12458,16 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="M139" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="N139" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -12490,16 +12502,16 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M140" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="N140" t="s">
-        <v>1457</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -12534,16 +12546,16 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M141" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="N141" t="s">
-        <v>1458</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -12578,16 +12590,16 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M142" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="N142" t="s">
-        <v>1459</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -12622,16 +12634,16 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="M143" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="N143" t="s">
-        <v>1460</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -12666,16 +12678,16 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M144" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N144" t="s">
-        <v>1461</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -12710,16 +12722,16 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M145" t="s">
         <v>516</v>
       </c>
       <c r="N145" t="s">
-        <v>1462</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="146" spans="1:14">
@@ -12754,16 +12766,16 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M146" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N146" t="s">
-        <v>1463</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -12798,16 +12810,16 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M147" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N147" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -12842,16 +12854,16 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M148" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="N148" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -12886,16 +12898,16 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M149" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N149" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -12930,16 +12942,16 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M150" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N150" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -12974,16 +12986,16 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M151" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N151" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -13018,16 +13030,16 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M152" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N152" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -13062,16 +13074,16 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M153" t="s">
         <v>518</v>
       </c>
       <c r="N153" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -13106,16 +13118,16 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M154" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N154" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -13150,16 +13162,16 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M155" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="N155" t="s">
-        <v>1472</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -13194,16 +13206,16 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M156" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="N156" t="s">
-        <v>1473</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -13238,16 +13250,16 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M157" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N157" t="s">
-        <v>1474</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="158" spans="1:14">
@@ -13282,16 +13294,16 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M158" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N158" t="s">
-        <v>1475</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="159" spans="1:14">
@@ -13326,16 +13338,16 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M159" t="s">
         <v>521</v>
       </c>
       <c r="N159" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -13370,16 +13382,16 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M160" t="s">
         <v>522</v>
       </c>
       <c r="N160" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="161" spans="1:14">
@@ -13414,16 +13426,16 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M161" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N161" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="162" spans="1:14">
@@ -13458,16 +13470,16 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M162" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N162" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -13502,16 +13514,16 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M163" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N163" t="s">
-        <v>1480</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="164" spans="1:14">
@@ -13546,16 +13558,16 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M164" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="N164" t="s">
-        <v>1481</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="165" spans="1:14">
@@ -13590,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M165" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N165" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -13634,16 +13646,16 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M166" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N166" t="s">
-        <v>1483</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="167" spans="1:14">
@@ -13678,16 +13690,16 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M167" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N167" t="s">
-        <v>1484</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="168" spans="1:14">
@@ -13722,16 +13734,16 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M168" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N168" t="s">
-        <v>1485</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="169" spans="1:14">
@@ -13766,16 +13778,16 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M169" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N169" t="s">
-        <v>1486</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="170" spans="1:14">
@@ -13810,16 +13822,16 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M170" t="s">
         <v>529</v>
       </c>
       <c r="N170" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -13854,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M171" t="s">
         <v>530</v>
       </c>
       <c r="N171" t="s">
-        <v>1488</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -13898,16 +13910,16 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M172" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N172" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="173" spans="1:14">
@@ -13942,16 +13954,16 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M173" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N173" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="174" spans="1:14">
@@ -13986,16 +13998,16 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M174" t="s">
         <v>533</v>
       </c>
       <c r="N174" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="175" spans="1:14">
@@ -14030,16 +14042,16 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M175" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N175" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="176" spans="1:14">
@@ -14074,16 +14086,16 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M176" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="N176" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -14118,16 +14130,16 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M177" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="N177" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="178" spans="1:14">
@@ -14162,16 +14174,16 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M178" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N178" t="s">
-        <v>1495</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="179" spans="1:14">
@@ -14206,16 +14218,16 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M179" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="N179" t="s">
-        <v>1496</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="180" spans="1:14">
@@ -14250,16 +14262,16 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M180" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N180" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="181" spans="1:14">
@@ -14294,16 +14306,16 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M181" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N181" t="s">
-        <v>1498</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="182" spans="1:14">
@@ -14338,16 +14350,16 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="M182" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N182" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="183" spans="1:14">
@@ -14382,16 +14394,16 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M183" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="N183" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="184" spans="1:14">
@@ -14426,16 +14438,16 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M184" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="N184" t="s">
-        <v>1501</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="185" spans="1:14">
@@ -14467,16 +14479,16 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M185" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="N185" t="s">
-        <v>1502</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="186" spans="1:14">
@@ -14511,16 +14523,16 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M186" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="N186" t="s">
-        <v>1503</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="187" spans="1:14">
@@ -14555,16 +14567,16 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M187" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="N187" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="188" spans="1:14">
@@ -14596,19 +14608,19 @@
         <v>7</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K188" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M188" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="N188" t="s">
-        <v>1505</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="189" spans="1:14">
@@ -14643,16 +14655,16 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M189" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N189" t="s">
-        <v>1506</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="190" spans="1:14">
@@ -14684,19 +14696,19 @@
         <v>0</v>
       </c>
       <c r="J190">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K190" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M190" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="N190" t="s">
-        <v>1507</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="191" spans="1:14">
@@ -14731,16 +14743,16 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M191" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="N191" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="192" spans="1:14">
@@ -14775,16 +14787,16 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M192" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="N192" t="s">
-        <v>1509</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="193" spans="1:14">
@@ -14819,16 +14831,16 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M193" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="N193" t="s">
-        <v>1510</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="194" spans="1:14">
@@ -14863,16 +14875,16 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M194" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="N194" t="s">
-        <v>1511</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="195" spans="1:14">
@@ -14907,16 +14919,16 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M195" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="N195" t="s">
-        <v>1512</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="196" spans="1:14">
@@ -14951,16 +14963,16 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M196" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="N196" t="s">
-        <v>1513</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="197" spans="1:14">
@@ -14995,16 +15007,16 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M197" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="N197" t="s">
-        <v>1514</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="198" spans="1:14">
@@ -15039,16 +15051,16 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M198" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N198" t="s">
-        <v>1515</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="199" spans="1:14">
@@ -15083,16 +15095,16 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M199" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N199" t="s">
-        <v>1516</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="200" spans="1:14">
@@ -15127,16 +15139,16 @@
         <v>5</v>
       </c>
       <c r="K200" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M200" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="N200" t="s">
-        <v>1517</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="201" spans="1:14">
@@ -15171,16 +15183,16 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M201" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="N201" t="s">
-        <v>1518</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="202" spans="1:14">
@@ -15215,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M202" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="N202" t="s">
-        <v>1519</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="203" spans="1:14">
@@ -15259,16 +15271,16 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M203" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="N203" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="204" spans="1:14">
@@ -15303,16 +15315,16 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M204" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N204" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="205" spans="1:14">
@@ -15347,16 +15359,16 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M205" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="N205" t="s">
-        <v>1522</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="206" spans="1:14">
@@ -15391,16 +15403,16 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M206" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N206" t="s">
-        <v>1523</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="207" spans="1:14">
@@ -15435,16 +15447,16 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M207" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N207" t="s">
-        <v>1524</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="208" spans="1:14">
@@ -15479,16 +15491,16 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M208" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N208" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="209" spans="1:14">
@@ -15523,16 +15535,16 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M209" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N209" t="s">
-        <v>1526</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="210" spans="1:14">
@@ -15567,16 +15579,16 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M210" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="N210" t="s">
-        <v>1527</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="211" spans="1:14">
@@ -15611,16 +15623,16 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M211" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="N211" t="s">
-        <v>1528</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="212" spans="1:14">
@@ -15655,16 +15667,16 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M212" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="N212" t="s">
-        <v>1529</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="213" spans="1:14">
@@ -15699,16 +15711,16 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M213" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="N213" t="s">
-        <v>1530</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="214" spans="1:14">
@@ -15743,16 +15755,16 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M214" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N214" t="s">
-        <v>1531</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="215" spans="1:14">
@@ -15787,16 +15799,16 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M215" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N215" t="s">
-        <v>1532</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="216" spans="1:14">
@@ -15831,16 +15843,16 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M216" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="N216" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="217" spans="1:14">
@@ -15875,16 +15887,16 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M217" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="N217" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="218" spans="1:14">
@@ -15919,16 +15931,16 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M218" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="N218" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="219" spans="1:14">
@@ -15963,16 +15975,16 @@
         <v>0</v>
       </c>
       <c r="K219" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M219" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="N219" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="220" spans="1:14">
@@ -16004,19 +16016,19 @@
         <v>0</v>
       </c>
       <c r="J220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K220" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M220" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="N220" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="221" spans="1:14">
@@ -16051,16 +16063,16 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M221" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N221" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="222" spans="1:14">
@@ -16089,19 +16101,19 @@
         <v>4</v>
       </c>
       <c r="J222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K222" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M222" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N222" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="223" spans="1:14">
@@ -16136,16 +16148,16 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M223" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="N223" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="224" spans="1:14">
@@ -16180,16 +16192,16 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M224" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="N224" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="225" spans="1:14">
@@ -16224,16 +16236,16 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M225" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="N225" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="226" spans="1:14">
@@ -16268,16 +16280,16 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M226" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="N226" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="227" spans="1:14">
@@ -16312,16 +16324,16 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M227" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="N227" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="228" spans="1:14">
@@ -16356,16 +16368,16 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M228" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="N228" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="229" spans="1:14">
@@ -16382,7 +16394,7 @@
         <v>580</v>
       </c>
       <c r="E229" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="F229">
         <v>3</v>
@@ -16397,19 +16409,19 @@
         <v>2</v>
       </c>
       <c r="J229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M229" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N229" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="230" spans="1:14">
@@ -16426,7 +16438,7 @@
         <v>581</v>
       </c>
       <c r="E230" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F230">
         <v>3</v>
@@ -16435,25 +16447,25 @@
         <v>0</v>
       </c>
       <c r="H230">
+        <v>1</v>
+      </c>
+      <c r="I230">
         <v>2</v>
       </c>
-      <c r="I230">
-        <v>1</v>
-      </c>
       <c r="J230">
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L230" s="1" t="s">
         <v>1011</v>
       </c>
       <c r="M230" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="N230" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="231" spans="1:14">
@@ -16470,7 +16482,7 @@
         <v>582</v>
       </c>
       <c r="E231" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F231">
         <v>3</v>
@@ -16479,25 +16491,25 @@
         <v>0</v>
       </c>
       <c r="H231">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231">
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>1002</v>
+        <v>1012</v>
       </c>
       <c r="M231" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="N231" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="232" spans="1:14">
@@ -16505,7 +16517,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C232" t="s">
         <v>314</v>
@@ -16513,6 +16525,9 @@
       <c r="D232" t="s">
         <v>583</v>
       </c>
+      <c r="E232" t="s">
+        <v>793</v>
+      </c>
       <c r="F232">
         <v>3</v>
       </c>
@@ -16520,25 +16535,25 @@
         <v>0</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I232">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J232">
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="M232" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="N232" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="233" spans="1:14">
@@ -16546,7 +16561,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C233" t="s">
         <v>315</v>
@@ -16554,11 +16569,8 @@
       <c r="D233" t="s">
         <v>584</v>
       </c>
-      <c r="E233" t="s">
-        <v>794</v>
-      </c>
       <c r="F233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -16567,22 +16579,22 @@
         <v>0</v>
       </c>
       <c r="I233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J233">
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>988</v>
+        <v>1013</v>
       </c>
       <c r="M233" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N233" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="234" spans="1:14">
@@ -16599,7 +16611,7 @@
         <v>585</v>
       </c>
       <c r="E234" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F234">
         <v>2</v>
@@ -16617,16 +16629,16 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="M234" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N234" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="235" spans="1:14">
@@ -16643,7 +16655,7 @@
         <v>586</v>
       </c>
       <c r="E235" t="s">
-        <v>758</v>
+        <v>795</v>
       </c>
       <c r="F235">
         <v>2</v>
@@ -16652,25 +16664,25 @@
         <v>0</v>
       </c>
       <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
         <v>2</v>
       </c>
-      <c r="I235">
-        <v>0</v>
-      </c>
       <c r="J235">
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="M235" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N235" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="236" spans="1:14">
@@ -16687,7 +16699,7 @@
         <v>587</v>
       </c>
       <c r="E236" t="s">
-        <v>796</v>
+        <v>758</v>
       </c>
       <c r="F236">
         <v>2</v>
@@ -16696,25 +16708,25 @@
         <v>0</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J236">
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>1013</v>
+        <v>986</v>
       </c>
       <c r="M236" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N236" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="237" spans="1:14">
@@ -16731,7 +16743,7 @@
         <v>588</v>
       </c>
       <c r="E237" t="s">
-        <v>755</v>
+        <v>796</v>
       </c>
       <c r="F237">
         <v>2</v>
@@ -16749,16 +16761,16 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="M237" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N237" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="238" spans="1:14">
@@ -16775,7 +16787,7 @@
         <v>589</v>
       </c>
       <c r="E238" t="s">
-        <v>797</v>
+        <v>699</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -16784,25 +16796,25 @@
         <v>0</v>
       </c>
       <c r="H238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>1014</v>
+        <v>992</v>
       </c>
       <c r="M238" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N238" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="239" spans="1:14">
@@ -16819,7 +16831,7 @@
         <v>590</v>
       </c>
       <c r="E239" t="s">
-        <v>798</v>
+        <v>755</v>
       </c>
       <c r="F239">
         <v>2</v>
@@ -16828,25 +16840,25 @@
         <v>0</v>
       </c>
       <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
         <v>2</v>
       </c>
-      <c r="I239">
-        <v>0</v>
-      </c>
       <c r="J239">
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>1003</v>
+        <v>983</v>
       </c>
       <c r="M239" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N239" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="240" spans="1:14">
@@ -16863,7 +16875,7 @@
         <v>591</v>
       </c>
       <c r="E240" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F240">
         <v>2</v>
@@ -16881,16 +16893,16 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="M240" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N240" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="241" spans="1:14">
@@ -16907,7 +16919,7 @@
         <v>592</v>
       </c>
       <c r="E241" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F241">
         <v>2</v>
@@ -16925,16 +16937,16 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>999</v>
+        <v>1004</v>
       </c>
       <c r="M241" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N241" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="242" spans="1:14">
@@ -16951,7 +16963,7 @@
         <v>593</v>
       </c>
       <c r="E242" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="F242">
         <v>2</v>
@@ -16969,16 +16981,16 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="M242" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="N242" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="243" spans="1:14">
@@ -16986,7 +16998,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C243" t="s">
         <v>325</v>
@@ -16995,7 +17007,7 @@
         <v>594</v>
       </c>
       <c r="E243" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F243">
         <v>2</v>
@@ -17004,25 +17016,25 @@
         <v>0</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I243">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J243">
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="M243" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N243" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="244" spans="1:14">
@@ -17030,7 +17042,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C244" t="s">
         <v>326</v>
@@ -17039,7 +17051,7 @@
         <v>595</v>
       </c>
       <c r="E244" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F244">
         <v>2</v>
@@ -17057,16 +17069,16 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M244" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N244" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="245" spans="1:14">
@@ -17082,6 +17094,9 @@
       <c r="D245" t="s">
         <v>596</v>
       </c>
+      <c r="E245" t="s">
+        <v>802</v>
+      </c>
       <c r="F245">
         <v>2</v>
       </c>
@@ -17089,25 +17104,25 @@
         <v>0</v>
       </c>
       <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
         <v>2</v>
       </c>
-      <c r="I245">
-        <v>0</v>
-      </c>
       <c r="J245">
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="M245" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N245" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="246" spans="1:14">
@@ -17115,7 +17130,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C246" t="s">
         <v>328</v>
@@ -17124,16 +17139,16 @@
         <v>597</v>
       </c>
       <c r="E246" t="s">
-        <v>772</v>
+        <v>803</v>
       </c>
       <c r="F246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G246">
         <v>0</v>
       </c>
       <c r="H246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I246">
         <v>0</v>
@@ -17142,16 +17157,16 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>994</v>
+        <v>1018</v>
       </c>
       <c r="M246" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N246" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="247" spans="1:14">
@@ -17159,7 +17174,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C247" t="s">
         <v>329</v>
@@ -17167,35 +17182,32 @@
       <c r="D247" t="s">
         <v>598</v>
       </c>
-      <c r="E247" t="s">
-        <v>804</v>
-      </c>
       <c r="F247">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G247">
         <v>0</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247">
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>983</v>
+        <v>1019</v>
       </c>
       <c r="M247" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N247" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="248" spans="1:14">
@@ -17212,7 +17224,7 @@
         <v>599</v>
       </c>
       <c r="E248" t="s">
-        <v>805</v>
+        <v>772</v>
       </c>
       <c r="F248">
         <v>1</v>
@@ -17230,16 +17242,16 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M248" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N248" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="249" spans="1:14">
@@ -17250,13 +17262,13 @@
         <v>154</v>
       </c>
       <c r="C249" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="D249" t="s">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="E249" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -17274,16 +17286,16 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>1019</v>
+        <v>984</v>
       </c>
       <c r="M249" t="s">
-        <v>1068</v>
+        <v>1254</v>
       </c>
       <c r="N249" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="250" spans="1:14">
@@ -17294,13 +17306,13 @@
         <v>154</v>
       </c>
       <c r="C250" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D250" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E250" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -17309,25 +17321,25 @@
         <v>0</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250">
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>1020</v>
+        <v>995</v>
       </c>
       <c r="M250" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="N250" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="251" spans="1:14">
@@ -17338,13 +17350,13 @@
         <v>154</v>
       </c>
       <c r="C251" t="s">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="D251" t="s">
-        <v>601</v>
+        <v>559</v>
       </c>
       <c r="E251" t="s">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -17353,25 +17365,25 @@
         <v>0</v>
       </c>
       <c r="H251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251">
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="M251" t="s">
-        <v>1254</v>
+        <v>1069</v>
       </c>
       <c r="N251" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="252" spans="1:14">
@@ -17388,7 +17400,7 @@
         <v>602</v>
       </c>
       <c r="E252" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -17406,16 +17418,16 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="M252" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N252" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="253" spans="1:14">
@@ -17432,7 +17444,7 @@
         <v>603</v>
       </c>
       <c r="E253" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -17441,25 +17453,25 @@
         <v>0</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J253">
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="M253" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="N253" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="254" spans="1:14">
@@ -17476,7 +17488,7 @@
         <v>604</v>
       </c>
       <c r="E254" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -17485,25 +17497,25 @@
         <v>0</v>
       </c>
       <c r="H254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J254">
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>988</v>
+        <v>1023</v>
       </c>
       <c r="M254" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="N254" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="255" spans="1:14">
@@ -17520,7 +17532,7 @@
         <v>605</v>
       </c>
       <c r="E255" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -17529,25 +17541,25 @@
         <v>0</v>
       </c>
       <c r="H255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J255">
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="M255" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="N255" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="256" spans="1:14">
@@ -17564,7 +17576,7 @@
         <v>606</v>
       </c>
       <c r="E256" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -17573,25 +17585,25 @@
         <v>0</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256">
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="M256" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="N256" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -17608,7 +17620,7 @@
         <v>607</v>
       </c>
       <c r="E257" t="s">
-        <v>733</v>
+        <v>810</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -17617,25 +17629,25 @@
         <v>0</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J257">
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>982</v>
+        <v>1024</v>
       </c>
       <c r="M257" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="N257" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="258" spans="1:14">
@@ -17652,7 +17664,7 @@
         <v>608</v>
       </c>
       <c r="E258" t="s">
-        <v>733</v>
+        <v>811</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -17661,25 +17673,25 @@
         <v>0</v>
       </c>
       <c r="H258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J258">
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>1014</v>
+        <v>986</v>
       </c>
       <c r="M258" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="N258" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="259" spans="1:14">
@@ -17696,7 +17708,7 @@
         <v>609</v>
       </c>
       <c r="E259" t="s">
-        <v>774</v>
+        <v>733</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -17714,16 +17726,16 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>996</v>
+        <v>983</v>
       </c>
       <c r="M259" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="N259" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="260" spans="1:14">
@@ -17740,7 +17752,7 @@
         <v>610</v>
       </c>
       <c r="E260" t="s">
-        <v>812</v>
+        <v>733</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -17758,16 +17770,16 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="M260" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N260" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="261" spans="1:14">
@@ -17784,7 +17796,7 @@
         <v>611</v>
       </c>
       <c r="E261" t="s">
-        <v>813</v>
+        <v>774</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -17793,25 +17805,25 @@
         <v>0</v>
       </c>
       <c r="H261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261">
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="M261" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="N261" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="262" spans="1:14">
@@ -17828,7 +17840,7 @@
         <v>612</v>
       </c>
       <c r="E262" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F262">
         <v>1</v>
@@ -17837,25 +17849,25 @@
         <v>0</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J262">
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L262" s="1" t="s">
         <v>1024</v>
       </c>
       <c r="M262" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N262" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="263" spans="1:14">
@@ -17872,7 +17884,7 @@
         <v>613</v>
       </c>
       <c r="E263" t="s">
-        <v>699</v>
+        <v>813</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -17890,16 +17902,16 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="M263" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="N263" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="264" spans="1:14">
@@ -17934,16 +17946,16 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M264" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N264" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="265" spans="1:14">
@@ -17960,7 +17972,7 @@
         <v>615</v>
       </c>
       <c r="E265" t="s">
-        <v>775</v>
+        <v>814</v>
       </c>
       <c r="F265">
         <v>1</v>
@@ -17969,25 +17981,25 @@
         <v>0</v>
       </c>
       <c r="H265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J265">
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>989</v>
+        <v>1025</v>
       </c>
       <c r="M265" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="N265" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="266" spans="1:14">
@@ -18004,7 +18016,7 @@
         <v>616</v>
       </c>
       <c r="E266" t="s">
-        <v>815</v>
+        <v>775</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -18022,16 +18034,16 @@
         <v>0</v>
       </c>
       <c r="K266" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>1013</v>
+        <v>990</v>
       </c>
       <c r="M266" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N266" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="267" spans="1:14">
@@ -18048,7 +18060,7 @@
         <v>617</v>
       </c>
       <c r="E267" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -18063,19 +18075,19 @@
         <v>0</v>
       </c>
       <c r="J267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>997</v>
+        <v>1014</v>
       </c>
       <c r="M267" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N267" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="268" spans="1:14">
@@ -18092,7 +18104,7 @@
         <v>618</v>
       </c>
       <c r="E268" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -18101,25 +18113,25 @@
         <v>0</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K268" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>1024</v>
+        <v>998</v>
       </c>
       <c r="M268" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N268" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="269" spans="1:14">
@@ -18136,7 +18148,7 @@
         <v>619</v>
       </c>
       <c r="E269" t="s">
-        <v>787</v>
+        <v>817</v>
       </c>
       <c r="F269">
         <v>1</v>
@@ -18154,16 +18166,16 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="M269" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N269" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="270" spans="1:14">
@@ -18180,7 +18192,7 @@
         <v>620</v>
       </c>
       <c r="E270" t="s">
-        <v>818</v>
+        <v>787</v>
       </c>
       <c r="F270">
         <v>1</v>
@@ -18189,25 +18201,25 @@
         <v>0</v>
       </c>
       <c r="H270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270">
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M270" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N270" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="271" spans="1:14">
@@ -18224,7 +18236,7 @@
         <v>621</v>
       </c>
       <c r="E271" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F271">
         <v>1</v>
@@ -18233,25 +18245,25 @@
         <v>0</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J271">
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="M271" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="N271" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="272" spans="1:14">
@@ -18268,7 +18280,7 @@
         <v>622</v>
       </c>
       <c r="E272" t="s">
-        <v>733</v>
+        <v>819</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -18277,25 +18289,25 @@
         <v>0</v>
       </c>
       <c r="H272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272">
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L272" s="1" t="s">
         <v>1014</v>
       </c>
       <c r="M272" t="s">
-        <v>1135</v>
+        <v>1276</v>
       </c>
       <c r="N272" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="273" spans="1:14">
@@ -18312,7 +18324,7 @@
         <v>623</v>
       </c>
       <c r="E273" t="s">
-        <v>820</v>
+        <v>733</v>
       </c>
       <c r="F273">
         <v>1</v>
@@ -18330,16 +18342,16 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>996</v>
+        <v>1015</v>
       </c>
       <c r="M273" t="s">
-        <v>1275</v>
+        <v>1136</v>
       </c>
       <c r="N273" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="274" spans="1:14">
@@ -18356,7 +18368,7 @@
         <v>624</v>
       </c>
       <c r="E274" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="F274">
         <v>1</v>
@@ -18374,16 +18386,16 @@
         <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L274" s="1" t="s">
         <v>997</v>
       </c>
       <c r="M274" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="N274" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="275" spans="1:14">
@@ -18400,7 +18412,7 @@
         <v>625</v>
       </c>
       <c r="E275" t="s">
-        <v>730</v>
+        <v>816</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -18418,16 +18430,16 @@
         <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>1013</v>
+        <v>998</v>
       </c>
       <c r="M275" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="N275" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="276" spans="1:14">
@@ -18444,7 +18456,7 @@
         <v>626</v>
       </c>
       <c r="E276" t="s">
-        <v>821</v>
+        <v>730</v>
       </c>
       <c r="F276">
         <v>1</v>
@@ -18453,25 +18465,25 @@
         <v>0</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I276">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276">
         <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="M276" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="N276" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="277" spans="1:14">
@@ -18488,7 +18500,7 @@
         <v>627</v>
       </c>
       <c r="E277" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -18497,25 +18509,25 @@
         <v>0</v>
       </c>
       <c r="H277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277">
         <v>0</v>
       </c>
       <c r="K277" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>985</v>
+        <v>1024</v>
       </c>
       <c r="M277" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N277" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="278" spans="1:14">
@@ -18532,7 +18544,7 @@
         <v>628</v>
       </c>
       <c r="E278" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="F278">
         <v>1</v>
@@ -18550,16 +18562,16 @@
         <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>1025</v>
+        <v>986</v>
       </c>
       <c r="M278" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N278" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="279" spans="1:14">
@@ -18576,7 +18588,7 @@
         <v>629</v>
       </c>
       <c r="E279" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -18585,25 +18597,25 @@
         <v>0</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I279">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279">
         <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L279" s="1" t="s">
         <v>1026</v>
       </c>
       <c r="M279" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="N279" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="280" spans="1:14">
@@ -18620,7 +18632,7 @@
         <v>630</v>
       </c>
       <c r="E280" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -18638,16 +18650,16 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L280" s="1" t="s">
         <v>1027</v>
       </c>
       <c r="M280" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N280" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="281" spans="1:14">
@@ -18664,7 +18676,7 @@
         <v>631</v>
       </c>
       <c r="E281" t="s">
-        <v>719</v>
+        <v>824</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -18682,16 +18694,16 @@
         <v>0</v>
       </c>
       <c r="K281" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L281" s="1" t="s">
         <v>1028</v>
       </c>
       <c r="M281" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="N281" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="282" spans="1:14">
@@ -18708,7 +18720,7 @@
         <v>632</v>
       </c>
       <c r="E282" t="s">
-        <v>825</v>
+        <v>719</v>
       </c>
       <c r="F282">
         <v>1</v>
@@ -18717,25 +18729,25 @@
         <v>0</v>
       </c>
       <c r="H282">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282">
         <v>0</v>
       </c>
       <c r="K282" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>991</v>
+        <v>1029</v>
       </c>
       <c r="M282" t="s">
-        <v>1080</v>
+        <v>1285</v>
       </c>
       <c r="N282" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="283" spans="1:14">
@@ -18752,7 +18764,7 @@
         <v>633</v>
       </c>
       <c r="E283" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -18761,25 +18773,25 @@
         <v>0</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J283">
         <v>0</v>
       </c>
       <c r="K283" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
       <c r="M283" t="s">
-        <v>1284</v>
+        <v>1081</v>
       </c>
       <c r="N283" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="284" spans="1:14">
@@ -18796,7 +18808,7 @@
         <v>634</v>
       </c>
       <c r="E284" t="s">
-        <v>699</v>
+        <v>814</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -18805,25 +18817,25 @@
         <v>0</v>
       </c>
       <c r="H284">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J284">
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>991</v>
+        <v>1025</v>
       </c>
       <c r="M284" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N284" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="285" spans="1:14">
@@ -18840,7 +18852,7 @@
         <v>635</v>
       </c>
       <c r="E285" t="s">
-        <v>816</v>
+        <v>699</v>
       </c>
       <c r="F285">
         <v>1</v>
@@ -18858,16 +18870,16 @@
         <v>0</v>
       </c>
       <c r="K285" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="M285" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="N285" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="286" spans="1:14">
@@ -18884,7 +18896,7 @@
         <v>636</v>
       </c>
       <c r="E286" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -18902,16 +18914,16 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>1025</v>
+        <v>998</v>
       </c>
       <c r="M286" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N286" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="287" spans="1:14">
@@ -18928,7 +18940,7 @@
         <v>637</v>
       </c>
       <c r="E287" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="F287">
         <v>1</v>
@@ -18937,25 +18949,25 @@
         <v>0</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287">
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>985</v>
+        <v>1026</v>
       </c>
       <c r="M287" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N287" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="288" spans="1:14">
@@ -18972,7 +18984,7 @@
         <v>638</v>
       </c>
       <c r="E288" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -18990,16 +19002,16 @@
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>1029</v>
+        <v>986</v>
       </c>
       <c r="M288" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N288" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="289" spans="1:14">
@@ -19016,7 +19028,7 @@
         <v>639</v>
       </c>
       <c r="E289" t="s">
-        <v>777</v>
+        <v>827</v>
       </c>
       <c r="F289">
         <v>1</v>
@@ -19025,25 +19037,25 @@
         <v>0</v>
       </c>
       <c r="H289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J289">
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>997</v>
+        <v>1030</v>
       </c>
       <c r="M289" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N289" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="290" spans="1:14">
@@ -19060,7 +19072,7 @@
         <v>640</v>
       </c>
       <c r="E290" t="s">
-        <v>828</v>
+        <v>777</v>
       </c>
       <c r="F290">
         <v>1</v>
@@ -19078,16 +19090,16 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="M290" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N290" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="291" spans="1:14">
@@ -19104,7 +19116,7 @@
         <v>641</v>
       </c>
       <c r="E291" t="s">
-        <v>775</v>
+        <v>828</v>
       </c>
       <c r="F291">
         <v>1</v>
@@ -19122,16 +19134,16 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="M291" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N291" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="292" spans="1:14">
@@ -19148,7 +19160,7 @@
         <v>642</v>
       </c>
       <c r="E292" t="s">
-        <v>829</v>
+        <v>775</v>
       </c>
       <c r="F292">
         <v>1</v>
@@ -19166,16 +19178,16 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>1023</v>
+        <v>990</v>
       </c>
       <c r="M292" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="N292" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="293" spans="1:14">
@@ -19210,16 +19222,16 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="M293" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N293" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="294" spans="1:14">
@@ -19236,7 +19248,7 @@
         <v>644</v>
       </c>
       <c r="E294" t="s">
-        <v>820</v>
+        <v>829</v>
       </c>
       <c r="F294">
         <v>1</v>
@@ -19245,25 +19257,25 @@
         <v>0</v>
       </c>
       <c r="H294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294">
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>996</v>
+        <v>1024</v>
       </c>
       <c r="M294" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="N294" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="295" spans="1:14">
@@ -19280,7 +19292,7 @@
         <v>645</v>
       </c>
       <c r="E295" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
       <c r="F295">
         <v>1</v>
@@ -19289,25 +19301,25 @@
         <v>0</v>
       </c>
       <c r="H295">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J295">
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>985</v>
+        <v>997</v>
       </c>
       <c r="M295" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="N295" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="296" spans="1:14">
@@ -19324,7 +19336,7 @@
         <v>646</v>
       </c>
       <c r="E296" t="s">
-        <v>765</v>
+        <v>830</v>
       </c>
       <c r="F296">
         <v>1</v>
@@ -19333,25 +19345,25 @@
         <v>0</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I296">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296">
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="M296" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="N296" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="297" spans="1:14">
@@ -19368,7 +19380,7 @@
         <v>647</v>
       </c>
       <c r="E297" t="s">
-        <v>831</v>
+        <v>765</v>
       </c>
       <c r="F297">
         <v>1</v>
@@ -19377,25 +19389,25 @@
         <v>0</v>
       </c>
       <c r="H297">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J297">
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M297" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N297" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="298" spans="1:14">
@@ -19412,7 +19424,7 @@
         <v>648</v>
       </c>
       <c r="E298" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="F298">
         <v>1</v>
@@ -19430,16 +19442,16 @@
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>992</v>
+        <v>1012</v>
       </c>
       <c r="M298" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N298" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="299" spans="1:14">
@@ -19456,7 +19468,7 @@
         <v>649</v>
       </c>
       <c r="E299" t="s">
-        <v>754</v>
+        <v>792</v>
       </c>
       <c r="F299">
         <v>1</v>
@@ -19465,25 +19477,25 @@
         <v>0</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I299">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J299">
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="M299" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N299" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="300" spans="1:14">
@@ -19500,7 +19512,7 @@
         <v>650</v>
       </c>
       <c r="E300" t="s">
-        <v>798</v>
+        <v>754</v>
       </c>
       <c r="F300">
         <v>1</v>
@@ -19518,16 +19530,16 @@
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="M300" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N300" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="301" spans="1:14">
@@ -19544,7 +19556,7 @@
         <v>651</v>
       </c>
       <c r="E301" t="s">
-        <v>832</v>
+        <v>798</v>
       </c>
       <c r="F301">
         <v>1</v>
@@ -19562,16 +19574,16 @@
         <v>0</v>
       </c>
       <c r="K301" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="M301" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N301" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="302" spans="1:14">
@@ -19588,7 +19600,7 @@
         <v>652</v>
       </c>
       <c r="E302" t="s">
-        <v>754</v>
+        <v>832</v>
       </c>
       <c r="F302">
         <v>1</v>
@@ -19606,16 +19618,16 @@
         <v>0</v>
       </c>
       <c r="K302" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>1004</v>
+        <v>1031</v>
       </c>
       <c r="M302" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N302" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="303" spans="1:14">
@@ -19632,7 +19644,7 @@
         <v>653</v>
       </c>
       <c r="E303" t="s">
-        <v>833</v>
+        <v>754</v>
       </c>
       <c r="F303">
         <v>1</v>
@@ -19650,16 +19662,16 @@
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M303" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="N303" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="304" spans="1:14">
@@ -19676,7 +19688,7 @@
         <v>654</v>
       </c>
       <c r="E304" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F304">
         <v>1</v>
@@ -19685,25 +19697,25 @@
         <v>0</v>
       </c>
       <c r="H304">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J304">
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>1031</v>
+        <v>1005</v>
       </c>
       <c r="M304" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N304" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="305" spans="1:14">
@@ -19720,7 +19732,7 @@
         <v>655</v>
       </c>
       <c r="E305" t="s">
-        <v>781</v>
+        <v>834</v>
       </c>
       <c r="F305">
         <v>1</v>
@@ -19738,16 +19750,16 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>998</v>
+        <v>1032</v>
       </c>
       <c r="M305" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="N305" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="306" spans="1:14">
@@ -19764,7 +19776,7 @@
         <v>656</v>
       </c>
       <c r="E306" t="s">
-        <v>835</v>
+        <v>781</v>
       </c>
       <c r="F306">
         <v>1</v>
@@ -19773,25 +19785,25 @@
         <v>0</v>
       </c>
       <c r="H306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L306" s="1" t="s">
         <v>999</v>
       </c>
       <c r="M306" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N306" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="307" spans="1:14">
@@ -19808,7 +19820,7 @@
         <v>657</v>
       </c>
       <c r="E307" t="s">
-        <v>798</v>
+        <v>835</v>
       </c>
       <c r="F307">
         <v>1</v>
@@ -19817,25 +19829,25 @@
         <v>0</v>
       </c>
       <c r="H307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="M307" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="N307" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="308" spans="1:14">
@@ -19852,7 +19864,7 @@
         <v>658</v>
       </c>
       <c r="E308" t="s">
-        <v>754</v>
+        <v>798</v>
       </c>
       <c r="F308">
         <v>1</v>
@@ -19861,25 +19873,25 @@
         <v>0</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I308">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J308">
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L308" s="1" t="s">
         <v>1004</v>
       </c>
       <c r="M308" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="N308" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="309" spans="1:14">
@@ -19896,7 +19908,7 @@
         <v>659</v>
       </c>
       <c r="E309" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="F309">
         <v>1</v>
@@ -19905,25 +19917,25 @@
         <v>0</v>
       </c>
       <c r="H309">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309">
         <v>0</v>
       </c>
       <c r="K309" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="M309" t="s">
-        <v>1135</v>
+        <v>1311</v>
       </c>
       <c r="N309" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="310" spans="1:14">
@@ -19958,16 +19970,16 @@
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M310" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="N310" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="311" spans="1:14">
@@ -20002,16 +20014,16 @@
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M311" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="N311" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="312" spans="1:14">
@@ -20046,16 +20058,16 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M312" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="N312" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="313" spans="1:14">
@@ -20090,16 +20102,16 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M313" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="N313" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="314" spans="1:14">
@@ -20134,16 +20146,16 @@
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M314" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="N314" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="315" spans="1:14">
@@ -20178,16 +20190,16 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M315" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="N315" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="316" spans="1:14">
@@ -20222,16 +20234,16 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M316" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="N316" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="317" spans="1:14">
@@ -20266,16 +20278,16 @@
         <v>0</v>
       </c>
       <c r="K317" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M317" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="N317" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="318" spans="1:14">
@@ -20310,16 +20322,16 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M318" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="N318" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="319" spans="1:14">
@@ -20354,16 +20366,16 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M319" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="N319" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="320" spans="1:14">
@@ -20398,16 +20410,16 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M320" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="N320" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="321" spans="1:14">
@@ -20442,16 +20454,16 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M321" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="N321" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="322" spans="1:14">
@@ -20486,16 +20498,16 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M322" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="N322" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="323" spans="1:14">
@@ -20512,7 +20524,7 @@
         <v>673</v>
       </c>
       <c r="E323" t="s">
-        <v>798</v>
+        <v>840</v>
       </c>
       <c r="F323">
         <v>1</v>
@@ -20530,16 +20542,16 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M323" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="N323" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="324" spans="1:14">
@@ -20574,16 +20586,16 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M324" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="N324" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="325" spans="1:14">
@@ -20618,16 +20630,16 @@
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M325" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="N325" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="326" spans="1:14">
@@ -20644,7 +20656,7 @@
         <v>676</v>
       </c>
       <c r="E326" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F326">
         <v>1</v>
@@ -20662,16 +20674,16 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M326" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="N326" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="327" spans="1:14">
@@ -20688,7 +20700,7 @@
         <v>677</v>
       </c>
       <c r="E327" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F327">
         <v>1</v>
@@ -20706,16 +20718,16 @@
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M327" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="N327" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="328" spans="1:14">
@@ -20750,16 +20762,16 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M328" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="N328" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="329" spans="1:14">
@@ -20794,16 +20806,16 @@
         <v>0</v>
       </c>
       <c r="K329" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M329" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="N329" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="330" spans="1:14">
@@ -20838,16 +20850,16 @@
         <v>0</v>
       </c>
       <c r="K330" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M330" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="N330" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="331" spans="1:14">
@@ -20858,13 +20870,13 @@
         <v>154</v>
       </c>
       <c r="C331" t="s">
-        <v>412</v>
+        <v>302</v>
       </c>
       <c r="D331" t="s">
-        <v>681</v>
+        <v>572</v>
       </c>
       <c r="E331" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="F331">
         <v>1</v>
@@ -20873,25 +20885,25 @@
         <v>0</v>
       </c>
       <c r="H331">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I331">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J331">
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="M331" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="N331" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="332" spans="1:14">
@@ -20902,13 +20914,13 @@
         <v>154</v>
       </c>
       <c r="C332" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D332" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E332" t="s">
-        <v>839</v>
+        <v>789</v>
       </c>
       <c r="F332">
         <v>1</v>
@@ -20926,16 +20938,16 @@
         <v>0</v>
       </c>
       <c r="K332" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>1034</v>
+        <v>1009</v>
       </c>
       <c r="M332" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="N332" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="333" spans="1:14">
@@ -20946,13 +20958,13 @@
         <v>154</v>
       </c>
       <c r="C333" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D333" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E333" t="s">
-        <v>784</v>
+        <v>839</v>
       </c>
       <c r="F333">
         <v>1</v>
@@ -20970,16 +20982,16 @@
         <v>0</v>
       </c>
       <c r="K333" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="M333" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="N333" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="334" spans="1:14">
@@ -20990,13 +21002,13 @@
         <v>154</v>
       </c>
       <c r="C334" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D334" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E334" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="F334">
         <v>1</v>
@@ -21014,16 +21026,16 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="M334" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="N334" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="335" spans="1:14">
@@ -21034,13 +21046,13 @@
         <v>154</v>
       </c>
       <c r="C335" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D335" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E335" t="s">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="F335">
         <v>1</v>
@@ -21058,16 +21070,16 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>1010</v>
+        <v>1033</v>
       </c>
       <c r="M335" t="s">
-        <v>1323</v>
+        <v>1336</v>
       </c>
       <c r="N335" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="336" spans="1:14">
@@ -21078,13 +21090,13 @@
         <v>154</v>
       </c>
       <c r="C336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D336" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E336" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F336">
         <v>1</v>
@@ -21102,16 +21114,16 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>992</v>
+        <v>1011</v>
       </c>
       <c r="M336" t="s">
-        <v>1334</v>
+        <v>1325</v>
       </c>
       <c r="N336" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="337" spans="1:14">
@@ -21122,13 +21134,13 @@
         <v>154</v>
       </c>
       <c r="C337" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D337" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E337" t="s">
-        <v>842</v>
+        <v>799</v>
       </c>
       <c r="F337">
         <v>1</v>
@@ -21146,16 +21158,16 @@
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="M337" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="N337" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="338" spans="1:14">
@@ -21163,13 +21175,13 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C338" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D338" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E338" t="s">
         <v>843</v>
@@ -21181,25 +21193,25 @@
         <v>0</v>
       </c>
       <c r="H338">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I338">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J338">
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>1035</v>
+        <v>1003</v>
       </c>
       <c r="M338" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="N338" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="339" spans="1:14">
@@ -21210,10 +21222,10 @@
         <v>152</v>
       </c>
       <c r="C339" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D339" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E339" t="s">
         <v>844</v>
@@ -21234,16 +21246,16 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L339" s="1" t="s">
         <v>1036</v>
       </c>
       <c r="M339" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="N339" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="340" spans="1:14">
@@ -21251,13 +21263,13 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="C340" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D340" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E340" t="s">
         <v>845</v>
@@ -21278,16 +21290,16 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>986</v>
+        <v>1037</v>
       </c>
       <c r="M340" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="N340" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="341" spans="1:14">
@@ -21295,19 +21307,19 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="C341" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D341" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E341" t="s">
         <v>846</v>
       </c>
       <c r="F341">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G341">
         <v>0</v>
@@ -21316,7 +21328,7 @@
         <v>0</v>
       </c>
       <c r="I341">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -21325,13 +21337,13 @@
         <v>850</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>1037</v>
+        <v>987</v>
       </c>
       <c r="M341" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="N341" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="342" spans="1:14">
@@ -21339,16 +21351,19 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C342" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D342" t="s">
-        <v>692</v>
+        <v>691</v>
+      </c>
+      <c r="E342" t="s">
+        <v>847</v>
       </c>
       <c r="F342">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G342">
         <v>0</v>
@@ -21357,7 +21372,7 @@
         <v>0</v>
       </c>
       <c r="I342">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -21369,10 +21384,10 @@
         <v>1038</v>
       </c>
       <c r="M342" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="N342" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="343" spans="1:14">
@@ -21383,13 +21398,10 @@
         <v>152</v>
       </c>
       <c r="C343" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D343" t="s">
-        <v>693</v>
-      </c>
-      <c r="E343" t="s">
-        <v>847</v>
+        <v>692</v>
       </c>
       <c r="F343">
         <v>1</v>
@@ -21407,16 +21419,16 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L343" s="1" t="s">
         <v>1039</v>
       </c>
       <c r="M343" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="N343" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="344" spans="1:14">
@@ -21424,16 +21436,16 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C344" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D344" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E344" t="s">
-        <v>742</v>
+        <v>848</v>
       </c>
       <c r="F344">
         <v>1</v>
@@ -21451,16 +21463,60 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L344" s="1" t="s">
         <v>1040</v>
       </c>
       <c r="M344" t="s">
-        <v>1135</v>
+        <v>1344</v>
       </c>
       <c r="N344" t="s">
-        <v>1661</v>
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345" t="s">
+        <v>153</v>
+      </c>
+      <c r="C345" t="s">
+        <v>425</v>
+      </c>
+      <c r="D345" t="s">
+        <v>694</v>
+      </c>
+      <c r="E345" t="s">
+        <v>742</v>
+      </c>
+      <c r="F345">
+        <v>1</v>
+      </c>
+      <c r="G345">
+        <v>0</v>
+      </c>
+      <c r="H345">
+        <v>0</v>
+      </c>
+      <c r="I345">
+        <v>1</v>
+      </c>
+      <c r="J345">
+        <v>0</v>
+      </c>
+      <c r="K345" t="s">
+        <v>852</v>
+      </c>
+      <c r="L345" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="M345" t="s">
+        <v>1136</v>
+      </c>
+      <c r="N345" t="s">
+        <v>1665</v>
       </c>
     </row>
   </sheetData>
@@ -21808,6 +21864,7 @@
     <hyperlink ref="L342" r:id="rId341"/>
     <hyperlink ref="L343" r:id="rId342"/>
     <hyperlink ref="L344" r:id="rId343"/>
+    <hyperlink ref="L345" r:id="rId344"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="s">
         <v>849</v>
@@ -15972,7 +15972,7 @@
         <v>0</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K219" t="s">
         <v>850</v>

--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -10684,7 +10684,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="s">
         <v>849</v>
@@ -14696,7 +14696,7 @@
         <v>0</v>
       </c>
       <c r="J190">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K190" t="s">
         <v>850</v>
@@ -15136,7 +15136,7 @@
         <v>2</v>
       </c>
       <c r="J200">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K200" t="s">
         <v>850</v>
@@ -16101,7 +16101,7 @@
         <v>4</v>
       </c>
       <c r="J222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K222" t="s">
         <v>850</v>
@@ -18119,7 +18119,7 @@
         <v>0</v>
       </c>
       <c r="J268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K268" t="s">
         <v>850</v>
@@ -19835,7 +19835,7 @@
         <v>1</v>
       </c>
       <c r="J307">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" t="s">
         <v>850</v>

--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1667">
   <si>
     <t>Measure</t>
   </si>
@@ -2407,6 +2407,9 @@
   </si>
   <si>
     <t>2025-01-24</t>
+  </si>
+  <si>
+    <t>2025-07-12</t>
   </si>
   <si>
     <t>2025-09-27</t>
@@ -6692,13 +6695,13 @@
         <v>84</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="M4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="N4" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -6736,13 +6739,13 @@
         <v>84</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M5" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="N5" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -6944,13 +6947,13 @@
         <v>84</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="M10" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="N10" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -6985,13 +6988,13 @@
         <v>84</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="M11" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="N11" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -7029,13 +7032,13 @@
         <v>84</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="M12" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="N12" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -7114,13 +7117,13 @@
         <v>84</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="M14" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N14" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -7158,13 +7161,13 @@
         <v>84</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M15" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="N15" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -7202,13 +7205,13 @@
         <v>84</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="M16" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="N16" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -7413,13 +7416,13 @@
         <v>84</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="M21" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N21" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -7457,13 +7460,13 @@
         <v>84</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="M22" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="N22" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -7498,13 +7501,13 @@
         <v>84</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M23" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="N23" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -7539,13 +7542,13 @@
         <v>84</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="M24" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="N24" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -7580,13 +7583,13 @@
         <v>84</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="M25" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="N25" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -7621,13 +7624,13 @@
         <v>84</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="M26" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="N26" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -7662,13 +7665,13 @@
         <v>84</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="M27" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="N27" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -7703,13 +7706,13 @@
         <v>84</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="M28" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="N28" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -7744,13 +7747,13 @@
         <v>84</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M29" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="N29" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -7788,13 +7791,13 @@
         <v>84</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="M30" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N30" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -7829,13 +7832,13 @@
         <v>84</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M31" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N31" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -7870,13 +7873,13 @@
         <v>84</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="M32" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N32" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -7911,13 +7914,13 @@
         <v>84</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="M33" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="N33" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -7952,13 +7955,13 @@
         <v>84</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M34" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="N34" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -7993,13 +7996,13 @@
         <v>84</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="M35" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N35" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -8547,13 +8550,13 @@
         <v>84</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="M48" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N48" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -8591,13 +8594,13 @@
         <v>84</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="M49" t="s">
         <v>440</v>
       </c>
       <c r="N49" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -8635,13 +8638,13 @@
         <v>84</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M50" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="N50" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -8679,13 +8682,13 @@
         <v>84</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M51" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="N51" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -8723,13 +8726,13 @@
         <v>84</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="M52" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="N52" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -8764,13 +8767,13 @@
         <v>84</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="M53" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="N53" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -8805,13 +8808,13 @@
         <v>84</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M54" t="s">
         <v>445</v>
       </c>
       <c r="N54" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -8846,13 +8849,13 @@
         <v>84</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="M55" t="s">
         <v>446</v>
       </c>
       <c r="N55" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -8890,13 +8893,13 @@
         <v>84</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="M56" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="N56" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -8931,13 +8934,13 @@
         <v>84</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="M57" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N57" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -8972,13 +8975,13 @@
         <v>84</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="M58" t="s">
         <v>448</v>
       </c>
       <c r="N58" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -9013,13 +9016,13 @@
         <v>84</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M59" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N59" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -9054,13 +9057,13 @@
         <v>84</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="M60" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N60" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -9095,13 +9098,13 @@
         <v>84</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="M61" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N61" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -9136,13 +9139,13 @@
         <v>84</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M62" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="N62" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -9177,13 +9180,13 @@
         <v>84</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="M63" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="N63" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -9218,13 +9221,13 @@
         <v>84</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="M64" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N64" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -9259,13 +9262,13 @@
         <v>84</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="M65" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="N65" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -9300,13 +9303,13 @@
         <v>84</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="M66" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N66" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -9341,13 +9344,13 @@
         <v>84</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="M67" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N67" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -9382,13 +9385,13 @@
         <v>84</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="M68" t="s">
         <v>451</v>
       </c>
       <c r="N68" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -9426,13 +9429,13 @@
         <v>84</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="M69" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="N69" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -9470,13 +9473,13 @@
         <v>84</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="M70" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N70" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -9514,13 +9517,13 @@
         <v>84</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M71" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="N71" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -9558,13 +9561,13 @@
         <v>84</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M72" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="N72" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -9602,13 +9605,13 @@
         <v>84</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="M73" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="N73" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -9646,13 +9649,13 @@
         <v>84</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="M74" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N74" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -9687,16 +9690,16 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M75" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N75" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -9731,16 +9734,16 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="M76" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="N76" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -9775,16 +9778,16 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M77" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="N77" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -9819,16 +9822,16 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="M78" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="N78" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -9863,16 +9866,16 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M79" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N79" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -9907,16 +9910,16 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M80" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N80" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -9951,16 +9954,16 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M81" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N81" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -9995,16 +9998,16 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M82" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N82" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -10039,16 +10042,16 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M83" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="N83" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -10080,16 +10083,16 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="M84" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="N84" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -10124,16 +10127,16 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M85" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="N85" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -10168,16 +10171,16 @@
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="M86" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N86" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -10212,16 +10215,16 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="M87" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="N87" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -10253,16 +10256,16 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="M88" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="N88" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -10297,16 +10300,16 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="M89" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="N89" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -10338,16 +10341,16 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="M90" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N90" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -10382,16 +10385,16 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="M91" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N91" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -10426,16 +10429,16 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M92" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="N92" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -10470,16 +10473,16 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M93" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N93" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -10514,16 +10517,16 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M94" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="N94" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -10558,16 +10561,16 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="M95" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="N95" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -10602,16 +10605,16 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="M96" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="N96" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -10643,16 +10646,16 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M97" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="N97" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -10687,16 +10690,16 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="M98" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N98" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -10728,16 +10731,16 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="M99" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="N99" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -10772,16 +10775,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="M100" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="N100" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -10816,16 +10819,16 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M101" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="N101" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -10860,16 +10863,16 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M102" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="N102" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -10904,16 +10907,16 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="M103" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="N103" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -10948,16 +10951,16 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="M104" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="N104" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -10992,16 +10995,16 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="M105" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="N105" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -11036,16 +11039,16 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="M106" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="N106" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -11080,16 +11083,16 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M107" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="N107" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -11124,16 +11127,16 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M108" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="N108" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -11168,16 +11171,16 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M109" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="N109" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -11212,16 +11215,16 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M110" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="N110" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -11256,16 +11259,16 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M111" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="N111" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -11300,16 +11303,16 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M112" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N112" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -11344,16 +11347,16 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M113" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="N113" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -11388,16 +11391,16 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M114" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="N114" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -11432,16 +11435,16 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="M115" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N115" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -11476,16 +11479,16 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M116" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N116" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -11520,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M117" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="N117" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -11561,16 +11564,16 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="M118" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="N118" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -11602,16 +11605,16 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="M119" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="N119" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -11646,16 +11649,16 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="M120" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="N120" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -11690,16 +11693,16 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M121" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="N121" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -11734,16 +11737,16 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M122" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="N122" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -11778,16 +11781,16 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M123" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="N123" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -11822,16 +11825,16 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="M124" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="N124" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -11866,16 +11869,16 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="M125" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="N125" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -11910,16 +11913,16 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M126" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N126" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -11954,16 +11957,16 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="M127" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N127" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -11998,16 +12001,16 @@
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M128" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="N128" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -12042,16 +12045,16 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="M129" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="N129" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -12083,16 +12086,16 @@
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="M130" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="N130" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -12124,16 +12127,16 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M131" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N131" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -12165,16 +12168,16 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="M132" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="N132" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -12206,16 +12209,16 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="M133" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="N133" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -12247,16 +12250,16 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="M134" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="N134" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -12288,16 +12291,16 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="M135" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="N135" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -12329,16 +12332,16 @@
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="M136" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="N136" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -12373,16 +12376,16 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="M137" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="N137" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -12417,16 +12420,16 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="M138" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="N138" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -12458,16 +12461,16 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M139" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="N139" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -12502,16 +12505,16 @@
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="M140" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="N140" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -12546,16 +12549,16 @@
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="M141" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="N141" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -12590,16 +12593,16 @@
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="M142" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="N142" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -12634,16 +12637,16 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M143" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N143" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -12678,16 +12681,16 @@
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M144" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N144" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -12722,16 +12725,16 @@
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M145" t="s">
         <v>516</v>
       </c>
       <c r="N145" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="146" spans="1:14">
@@ -12766,16 +12769,16 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M146" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N146" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -12810,16 +12813,16 @@
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M147" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="N147" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -12854,16 +12857,16 @@
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M148" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N148" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -12898,16 +12901,16 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="M149" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N149" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -12942,16 +12945,16 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="M150" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N150" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -12986,16 +12989,16 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M151" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N151" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -13030,16 +13033,16 @@
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="M152" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N152" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -13074,16 +13077,16 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="M153" t="s">
         <v>518</v>
       </c>
       <c r="N153" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -13118,16 +13121,16 @@
         <v>0</v>
       </c>
       <c r="K154" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M154" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="N154" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -13162,16 +13165,16 @@
         <v>0</v>
       </c>
       <c r="K155" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M155" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="N155" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -13206,16 +13209,16 @@
         <v>0</v>
       </c>
       <c r="K156" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M156" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N156" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -13250,16 +13253,16 @@
         <v>0</v>
       </c>
       <c r="K157" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M157" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N157" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="158" spans="1:14">
@@ -13294,16 +13297,16 @@
         <v>0</v>
       </c>
       <c r="K158" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="M158" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N158" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="159" spans="1:14">
@@ -13338,16 +13341,16 @@
         <v>0</v>
       </c>
       <c r="K159" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M159" t="s">
         <v>521</v>
       </c>
       <c r="N159" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -13382,16 +13385,16 @@
         <v>0</v>
       </c>
       <c r="K160" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M160" t="s">
         <v>522</v>
       </c>
       <c r="N160" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="161" spans="1:14">
@@ -13426,16 +13429,16 @@
         <v>0</v>
       </c>
       <c r="K161" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M161" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N161" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="162" spans="1:14">
@@ -13470,16 +13473,16 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="M162" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N162" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -13514,16 +13517,16 @@
         <v>0</v>
       </c>
       <c r="K163" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M163" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="N163" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="164" spans="1:14">
@@ -13558,16 +13561,16 @@
         <v>0</v>
       </c>
       <c r="K164" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M164" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N164" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="165" spans="1:14">
@@ -13602,16 +13605,16 @@
         <v>0</v>
       </c>
       <c r="K165" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="M165" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N165" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -13646,16 +13649,16 @@
         <v>0</v>
       </c>
       <c r="K166" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M166" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N166" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="167" spans="1:14">
@@ -13690,16 +13693,16 @@
         <v>0</v>
       </c>
       <c r="K167" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="M167" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N167" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="168" spans="1:14">
@@ -13734,16 +13737,16 @@
         <v>0</v>
       </c>
       <c r="K168" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M168" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N168" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="169" spans="1:14">
@@ -13778,16 +13781,16 @@
         <v>0</v>
       </c>
       <c r="K169" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M169" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N169" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="170" spans="1:14">
@@ -13822,16 +13825,16 @@
         <v>0</v>
       </c>
       <c r="K170" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M170" t="s">
         <v>529</v>
       </c>
       <c r="N170" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -13866,16 +13869,16 @@
         <v>0</v>
       </c>
       <c r="K171" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M171" t="s">
         <v>530</v>
       </c>
       <c r="N171" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -13910,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="K172" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M172" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N172" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="173" spans="1:14">
@@ -13954,16 +13957,16 @@
         <v>0</v>
       </c>
       <c r="K173" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M173" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N173" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="174" spans="1:14">
@@ -13998,16 +14001,16 @@
         <v>0</v>
       </c>
       <c r="K174" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="M174" t="s">
         <v>533</v>
       </c>
       <c r="N174" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="175" spans="1:14">
@@ -14042,16 +14045,16 @@
         <v>0</v>
       </c>
       <c r="K175" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M175" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="N175" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="176" spans="1:14">
@@ -14086,16 +14089,16 @@
         <v>0</v>
       </c>
       <c r="K176" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M176" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="N176" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -14130,16 +14133,16 @@
         <v>0</v>
       </c>
       <c r="K177" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M177" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N177" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="178" spans="1:14">
@@ -14174,16 +14177,16 @@
         <v>0</v>
       </c>
       <c r="K178" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="M178" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="N178" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="179" spans="1:14">
@@ -14218,16 +14221,16 @@
         <v>0</v>
       </c>
       <c r="K179" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="M179" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N179" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="180" spans="1:14">
@@ -14262,16 +14265,16 @@
         <v>0</v>
       </c>
       <c r="K180" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M180" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N180" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="181" spans="1:14">
@@ -14306,16 +14309,16 @@
         <v>0</v>
       </c>
       <c r="K181" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="M181" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N181" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="182" spans="1:14">
@@ -14350,16 +14353,16 @@
         <v>0</v>
       </c>
       <c r="K182" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="M182" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="N182" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="183" spans="1:14">
@@ -14394,16 +14397,16 @@
         <v>0</v>
       </c>
       <c r="K183" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M183" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="N183" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="184" spans="1:14">
@@ -14438,16 +14441,16 @@
         <v>0</v>
       </c>
       <c r="K184" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="M184" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="N184" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="185" spans="1:14">
@@ -14479,16 +14482,16 @@
         <v>0</v>
       </c>
       <c r="K185" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="M185" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="N185" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="186" spans="1:14">
@@ -14523,16 +14526,16 @@
         <v>0</v>
       </c>
       <c r="K186" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="M186" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="N186" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="187" spans="1:14">
@@ -14567,16 +14570,16 @@
         <v>0</v>
       </c>
       <c r="K187" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M187" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="N187" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="188" spans="1:14">
@@ -14611,16 +14614,16 @@
         <v>2</v>
       </c>
       <c r="K188" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M188" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N188" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="189" spans="1:14">
@@ -14655,16 +14658,16 @@
         <v>0</v>
       </c>
       <c r="K189" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M189" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="N189" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="190" spans="1:14">
@@ -14699,16 +14702,16 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="M190" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="N190" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="191" spans="1:14">
@@ -14743,16 +14746,16 @@
         <v>0</v>
       </c>
       <c r="K191" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M191" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="N191" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="192" spans="1:14">
@@ -14787,16 +14790,16 @@
         <v>0</v>
       </c>
       <c r="K192" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M192" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="N192" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="193" spans="1:14">
@@ -14831,16 +14834,16 @@
         <v>0</v>
       </c>
       <c r="K193" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="M193" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="N193" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="194" spans="1:14">
@@ -14875,16 +14878,16 @@
         <v>0</v>
       </c>
       <c r="K194" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M194" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="N194" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="195" spans="1:14">
@@ -14919,16 +14922,16 @@
         <v>0</v>
       </c>
       <c r="K195" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M195" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="N195" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="196" spans="1:14">
@@ -14963,16 +14966,16 @@
         <v>0</v>
       </c>
       <c r="K196" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M196" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="N196" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="197" spans="1:14">
@@ -15007,16 +15010,16 @@
         <v>0</v>
       </c>
       <c r="K197" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M197" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N197" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="198" spans="1:14">
@@ -15051,16 +15054,16 @@
         <v>0</v>
       </c>
       <c r="K198" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M198" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N198" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="199" spans="1:14">
@@ -15095,16 +15098,16 @@
         <v>0</v>
       </c>
       <c r="K199" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M199" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="N199" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="200" spans="1:14">
@@ -15139,16 +15142,16 @@
         <v>0</v>
       </c>
       <c r="K200" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M200" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="N200" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="201" spans="1:14">
@@ -15183,16 +15186,16 @@
         <v>0</v>
       </c>
       <c r="K201" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L201" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M201" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="N201" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="202" spans="1:14">
@@ -15227,16 +15230,16 @@
         <v>0</v>
       </c>
       <c r="K202" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L202" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="M202" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="N202" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="203" spans="1:14">
@@ -15271,16 +15274,16 @@
         <v>0</v>
       </c>
       <c r="K203" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M203" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N203" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="204" spans="1:14">
@@ -15315,16 +15318,16 @@
         <v>0</v>
       </c>
       <c r="K204" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M204" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="N204" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="205" spans="1:14">
@@ -15359,16 +15362,16 @@
         <v>0</v>
       </c>
       <c r="K205" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="M205" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N205" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="206" spans="1:14">
@@ -15403,16 +15406,16 @@
         <v>0</v>
       </c>
       <c r="K206" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L206" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M206" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N206" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="207" spans="1:14">
@@ -15447,16 +15450,16 @@
         <v>0</v>
       </c>
       <c r="K207" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L207" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M207" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N207" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="208" spans="1:14">
@@ -15491,16 +15494,16 @@
         <v>0</v>
       </c>
       <c r="K208" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M208" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N208" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="209" spans="1:14">
@@ -15535,16 +15538,16 @@
         <v>0</v>
       </c>
       <c r="K209" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L209" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M209" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="N209" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="210" spans="1:14">
@@ -15579,16 +15582,16 @@
         <v>0</v>
       </c>
       <c r="K210" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M210" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="N210" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="211" spans="1:14">
@@ -15623,16 +15626,16 @@
         <v>0</v>
       </c>
       <c r="K211" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M211" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="N211" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="212" spans="1:14">
@@ -15667,16 +15670,16 @@
         <v>0</v>
       </c>
       <c r="K212" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M212" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="N212" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="213" spans="1:14">
@@ -15711,16 +15714,16 @@
         <v>0</v>
       </c>
       <c r="K213" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M213" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="N213" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="214" spans="1:14">
@@ -15755,16 +15758,16 @@
         <v>0</v>
       </c>
       <c r="K214" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L214" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M214" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N214" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="215" spans="1:14">
@@ -15799,16 +15802,16 @@
         <v>0</v>
       </c>
       <c r="K215" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M215" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="N215" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="216" spans="1:14">
@@ -15843,16 +15846,16 @@
         <v>0</v>
       </c>
       <c r="K216" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M216" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="N216" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="217" spans="1:14">
@@ -15887,16 +15890,16 @@
         <v>0</v>
       </c>
       <c r="K217" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L217" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M217" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="N217" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="218" spans="1:14">
@@ -15931,16 +15934,16 @@
         <v>0</v>
       </c>
       <c r="K218" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="M218" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="N218" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="219" spans="1:14">
@@ -15975,16 +15978,16 @@
         <v>4</v>
       </c>
       <c r="K219" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M219" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="N219" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="220" spans="1:14">
@@ -16019,16 +16022,16 @@
         <v>2</v>
       </c>
       <c r="K220" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M220" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N220" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="221" spans="1:14">
@@ -16063,16 +16066,16 @@
         <v>0</v>
       </c>
       <c r="K221" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M221" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="N221" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="222" spans="1:14">
@@ -16104,16 +16107,16 @@
         <v>0</v>
       </c>
       <c r="K222" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M222" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="N222" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="223" spans="1:14">
@@ -16148,16 +16151,16 @@
         <v>0</v>
       </c>
       <c r="K223" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M223" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="N223" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="224" spans="1:14">
@@ -16192,16 +16195,16 @@
         <v>0</v>
       </c>
       <c r="K224" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M224" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="N224" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="225" spans="1:14">
@@ -16236,16 +16239,16 @@
         <v>0</v>
       </c>
       <c r="K225" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="M225" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="N225" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="226" spans="1:14">
@@ -16280,16 +16283,16 @@
         <v>0</v>
       </c>
       <c r="K226" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M226" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="N226" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="227" spans="1:14">
@@ -16324,16 +16327,16 @@
         <v>0</v>
       </c>
       <c r="K227" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M227" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="N227" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="228" spans="1:14">
@@ -16368,16 +16371,16 @@
         <v>0</v>
       </c>
       <c r="K228" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L228" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M228" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N228" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="229" spans="1:14">
@@ -16412,16 +16415,16 @@
         <v>1</v>
       </c>
       <c r="K229" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M229" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="N229" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="230" spans="1:14">
@@ -16456,16 +16459,16 @@
         <v>0</v>
       </c>
       <c r="K230" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M230" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="N230" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="231" spans="1:14">
@@ -16500,16 +16503,16 @@
         <v>0</v>
       </c>
       <c r="K231" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M231" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="N231" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="232" spans="1:14">
@@ -16544,16 +16547,16 @@
         <v>0</v>
       </c>
       <c r="K232" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M232" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N232" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="233" spans="1:14">
@@ -16585,16 +16588,16 @@
         <v>0</v>
       </c>
       <c r="K233" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="M233" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N233" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="234" spans="1:14">
@@ -16629,16 +16632,16 @@
         <v>0</v>
       </c>
       <c r="K234" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M234" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N234" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="235" spans="1:14">
@@ -16673,16 +16676,16 @@
         <v>0</v>
       </c>
       <c r="K235" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L235" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M235" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N235" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="236" spans="1:14">
@@ -16717,16 +16720,16 @@
         <v>0</v>
       </c>
       <c r="K236" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M236" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N236" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="237" spans="1:14">
@@ -16761,16 +16764,16 @@
         <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L237" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M237" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N237" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="238" spans="1:14">
@@ -16787,7 +16790,7 @@
         <v>589</v>
       </c>
       <c r="E238" t="s">
-        <v>699</v>
+        <v>797</v>
       </c>
       <c r="F238">
         <v>2</v>
@@ -16796,25 +16799,25 @@
         <v>0</v>
       </c>
       <c r="H238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J238">
         <v>1</v>
       </c>
       <c r="K238" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M238" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="N238" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="239" spans="1:14">
@@ -16849,16 +16852,16 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L239" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M239" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N239" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="240" spans="1:14">
@@ -16875,7 +16878,7 @@
         <v>591</v>
       </c>
       <c r="E240" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F240">
         <v>2</v>
@@ -16893,16 +16896,16 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M240" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="N240" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="241" spans="1:14">
@@ -16919,7 +16922,7 @@
         <v>592</v>
       </c>
       <c r="E241" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F241">
         <v>2</v>
@@ -16937,16 +16940,16 @@
         <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M241" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="N241" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="242" spans="1:14">
@@ -16963,7 +16966,7 @@
         <v>593</v>
       </c>
       <c r="E242" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F242">
         <v>2</v>
@@ -16981,16 +16984,16 @@
         <v>0</v>
       </c>
       <c r="K242" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M242" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N242" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="243" spans="1:14">
@@ -17007,7 +17010,7 @@
         <v>594</v>
       </c>
       <c r="E243" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F243">
         <v>2</v>
@@ -17025,16 +17028,16 @@
         <v>0</v>
       </c>
       <c r="K243" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M243" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N243" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="244" spans="1:14">
@@ -17051,7 +17054,7 @@
         <v>595</v>
       </c>
       <c r="E244" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F244">
         <v>2</v>
@@ -17069,16 +17072,16 @@
         <v>0</v>
       </c>
       <c r="K244" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="M244" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="N244" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="245" spans="1:14">
@@ -17095,7 +17098,7 @@
         <v>596</v>
       </c>
       <c r="E245" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F245">
         <v>2</v>
@@ -17113,16 +17116,16 @@
         <v>0</v>
       </c>
       <c r="K245" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="M245" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N245" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="246" spans="1:14">
@@ -17139,7 +17142,7 @@
         <v>597</v>
       </c>
       <c r="E246" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F246">
         <v>2</v>
@@ -17157,16 +17160,16 @@
         <v>0</v>
       </c>
       <c r="K246" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L246" s="1" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="M246" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="N246" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="247" spans="1:14">
@@ -17198,16 +17201,16 @@
         <v>0</v>
       </c>
       <c r="K247" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="M247" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N247" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="248" spans="1:14">
@@ -17242,16 +17245,16 @@
         <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M248" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="N248" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="249" spans="1:14">
@@ -17268,7 +17271,7 @@
         <v>600</v>
       </c>
       <c r="E249" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -17286,16 +17289,16 @@
         <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="M249" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="N249" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="250" spans="1:14">
@@ -17312,7 +17315,7 @@
         <v>601</v>
       </c>
       <c r="E250" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -17330,16 +17333,16 @@
         <v>0</v>
       </c>
       <c r="K250" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M250" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="N250" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="251" spans="1:14">
@@ -17374,16 +17377,16 @@
         <v>0</v>
       </c>
       <c r="K251" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="M251" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="N251" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="252" spans="1:14">
@@ -17400,7 +17403,7 @@
         <v>602</v>
       </c>
       <c r="E252" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -17418,16 +17421,16 @@
         <v>0</v>
       </c>
       <c r="K252" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M252" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="N252" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="253" spans="1:14">
@@ -17444,7 +17447,7 @@
         <v>603</v>
       </c>
       <c r="E253" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -17462,16 +17465,16 @@
         <v>0</v>
       </c>
       <c r="K253" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M253" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="N253" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="254" spans="1:14">
@@ -17488,7 +17491,7 @@
         <v>604</v>
       </c>
       <c r="E254" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -17506,16 +17509,16 @@
         <v>0</v>
       </c>
       <c r="K254" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="M254" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="N254" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="255" spans="1:14">
@@ -17532,7 +17535,7 @@
         <v>605</v>
       </c>
       <c r="E255" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -17550,16 +17553,16 @@
         <v>0</v>
       </c>
       <c r="K255" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="M255" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="N255" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="256" spans="1:14">
@@ -17576,7 +17579,7 @@
         <v>606</v>
       </c>
       <c r="E256" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -17594,16 +17597,16 @@
         <v>0</v>
       </c>
       <c r="K256" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M256" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="N256" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -17620,7 +17623,7 @@
         <v>607</v>
       </c>
       <c r="E257" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -17638,16 +17641,16 @@
         <v>0</v>
       </c>
       <c r="K257" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M257" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="N257" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="258" spans="1:14">
@@ -17664,7 +17667,7 @@
         <v>608</v>
       </c>
       <c r="E258" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -17682,16 +17685,16 @@
         <v>0</v>
       </c>
       <c r="K258" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M258" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="N258" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="259" spans="1:14">
@@ -17726,16 +17729,16 @@
         <v>0</v>
       </c>
       <c r="K259" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="M259" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N259" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="260" spans="1:14">
@@ -17770,16 +17773,16 @@
         <v>0</v>
       </c>
       <c r="K260" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M260" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="N260" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="261" spans="1:14">
@@ -17814,16 +17817,16 @@
         <v>0</v>
       </c>
       <c r="K261" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M261" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N261" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="262" spans="1:14">
@@ -17840,7 +17843,7 @@
         <v>612</v>
       </c>
       <c r="E262" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F262">
         <v>1</v>
@@ -17858,16 +17861,16 @@
         <v>0</v>
       </c>
       <c r="K262" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M262" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="N262" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="263" spans="1:14">
@@ -17884,7 +17887,7 @@
         <v>613</v>
       </c>
       <c r="E263" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -17902,16 +17905,16 @@
         <v>0</v>
       </c>
       <c r="K263" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M263" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N263" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="264" spans="1:14">
@@ -17928,7 +17931,7 @@
         <v>614</v>
       </c>
       <c r="E264" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F264">
         <v>1</v>
@@ -17946,16 +17949,16 @@
         <v>0</v>
       </c>
       <c r="K264" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M264" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="N264" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="265" spans="1:14">
@@ -17972,7 +17975,7 @@
         <v>615</v>
       </c>
       <c r="E265" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F265">
         <v>1</v>
@@ -17990,16 +17993,16 @@
         <v>0</v>
       </c>
       <c r="K265" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M265" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N265" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="266" spans="1:14">
@@ -18034,16 +18037,16 @@
         <v>0</v>
       </c>
       <c r="K266" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M266" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N266" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="267" spans="1:14">
@@ -18060,7 +18063,7 @@
         <v>617</v>
       </c>
       <c r="E267" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -18078,16 +18081,16 @@
         <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M267" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N267" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="268" spans="1:14">
@@ -18104,7 +18107,7 @@
         <v>618</v>
       </c>
       <c r="E268" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -18122,16 +18125,16 @@
         <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M268" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N268" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="269" spans="1:14">
@@ -18148,7 +18151,7 @@
         <v>619</v>
       </c>
       <c r="E269" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F269">
         <v>1</v>
@@ -18166,16 +18169,16 @@
         <v>0</v>
       </c>
       <c r="K269" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M269" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N269" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="270" spans="1:14">
@@ -18210,16 +18213,16 @@
         <v>0</v>
       </c>
       <c r="K270" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M270" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="N270" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="271" spans="1:14">
@@ -18236,7 +18239,7 @@
         <v>621</v>
       </c>
       <c r="E271" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F271">
         <v>1</v>
@@ -18254,16 +18257,16 @@
         <v>0</v>
       </c>
       <c r="K271" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="M271" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="N271" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="272" spans="1:14">
@@ -18280,7 +18283,7 @@
         <v>622</v>
       </c>
       <c r="E272" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -18298,16 +18301,16 @@
         <v>0</v>
       </c>
       <c r="K272" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M272" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="N272" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="273" spans="1:14">
@@ -18342,16 +18345,16 @@
         <v>0</v>
       </c>
       <c r="K273" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M273" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="N273" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="274" spans="1:14">
@@ -18368,7 +18371,7 @@
         <v>624</v>
       </c>
       <c r="E274" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F274">
         <v>1</v>
@@ -18386,16 +18389,16 @@
         <v>0</v>
       </c>
       <c r="K274" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L274" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M274" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="N274" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="275" spans="1:14">
@@ -18412,7 +18415,7 @@
         <v>625</v>
       </c>
       <c r="E275" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -18430,16 +18433,16 @@
         <v>0</v>
       </c>
       <c r="K275" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L275" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M275" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="N275" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="276" spans="1:14">
@@ -18474,16 +18477,16 @@
         <v>0</v>
       </c>
       <c r="K276" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M276" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N276" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="277" spans="1:14">
@@ -18500,7 +18503,7 @@
         <v>627</v>
       </c>
       <c r="E277" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -18518,16 +18521,16 @@
         <v>0</v>
       </c>
       <c r="K277" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M277" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="N277" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="278" spans="1:14">
@@ -18544,7 +18547,7 @@
         <v>628</v>
       </c>
       <c r="E278" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F278">
         <v>1</v>
@@ -18562,16 +18565,16 @@
         <v>0</v>
       </c>
       <c r="K278" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M278" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="N278" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="279" spans="1:14">
@@ -18588,7 +18591,7 @@
         <v>629</v>
       </c>
       <c r="E279" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -18606,16 +18609,16 @@
         <v>0</v>
       </c>
       <c r="K279" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L279" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M279" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N279" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="280" spans="1:14">
@@ -18632,7 +18635,7 @@
         <v>630</v>
       </c>
       <c r="E280" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -18650,16 +18653,16 @@
         <v>0</v>
       </c>
       <c r="K280" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M280" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="N280" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="281" spans="1:14">
@@ -18676,7 +18679,7 @@
         <v>631</v>
       </c>
       <c r="E281" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -18694,16 +18697,16 @@
         <v>0</v>
       </c>
       <c r="K281" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L281" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="M281" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="N281" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="282" spans="1:14">
@@ -18738,16 +18741,16 @@
         <v>0</v>
       </c>
       <c r="K282" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L282" s="1" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="M282" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N282" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="283" spans="1:14">
@@ -18764,7 +18767,7 @@
         <v>633</v>
       </c>
       <c r="E283" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -18782,16 +18785,16 @@
         <v>0</v>
       </c>
       <c r="K283" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L283" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M283" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="N283" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="284" spans="1:14">
@@ -18808,7 +18811,7 @@
         <v>634</v>
       </c>
       <c r="E284" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -18826,16 +18829,16 @@
         <v>0</v>
       </c>
       <c r="K284" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="M284" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="N284" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="285" spans="1:14">
@@ -18870,16 +18873,16 @@
         <v>0</v>
       </c>
       <c r="K285" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="M285" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N285" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="286" spans="1:14">
@@ -18896,7 +18899,7 @@
         <v>636</v>
       </c>
       <c r="E286" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F286">
         <v>1</v>
@@ -18914,16 +18917,16 @@
         <v>0</v>
       </c>
       <c r="K286" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M286" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N286" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="287" spans="1:14">
@@ -18940,7 +18943,7 @@
         <v>637</v>
       </c>
       <c r="E287" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="F287">
         <v>1</v>
@@ -18958,16 +18961,16 @@
         <v>0</v>
       </c>
       <c r="K287" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="M287" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N287" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="288" spans="1:14">
@@ -18984,7 +18987,7 @@
         <v>638</v>
       </c>
       <c r="E288" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F288">
         <v>1</v>
@@ -19002,16 +19005,16 @@
         <v>0</v>
       </c>
       <c r="K288" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M288" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N288" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="289" spans="1:14">
@@ -19028,7 +19031,7 @@
         <v>639</v>
       </c>
       <c r="E289" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F289">
         <v>1</v>
@@ -19046,16 +19049,16 @@
         <v>0</v>
       </c>
       <c r="K289" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="M289" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N289" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="290" spans="1:14">
@@ -19090,16 +19093,16 @@
         <v>0</v>
       </c>
       <c r="K290" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L290" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M290" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N290" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="291" spans="1:14">
@@ -19116,7 +19119,7 @@
         <v>641</v>
       </c>
       <c r="E291" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F291">
         <v>1</v>
@@ -19134,16 +19137,16 @@
         <v>0</v>
       </c>
       <c r="K291" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L291" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M291" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="N291" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="292" spans="1:14">
@@ -19178,16 +19181,16 @@
         <v>0</v>
       </c>
       <c r="K292" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L292" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M292" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N292" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="293" spans="1:14">
@@ -19204,7 +19207,7 @@
         <v>643</v>
       </c>
       <c r="E293" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F293">
         <v>1</v>
@@ -19222,16 +19225,16 @@
         <v>0</v>
       </c>
       <c r="K293" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L293" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M293" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="N293" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="294" spans="1:14">
@@ -19248,7 +19251,7 @@
         <v>644</v>
       </c>
       <c r="E294" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F294">
         <v>1</v>
@@ -19266,16 +19269,16 @@
         <v>0</v>
       </c>
       <c r="K294" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L294" s="1" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="M294" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="N294" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="295" spans="1:14">
@@ -19292,7 +19295,7 @@
         <v>645</v>
       </c>
       <c r="E295" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F295">
         <v>1</v>
@@ -19310,16 +19313,16 @@
         <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L295" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="M295" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="N295" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="296" spans="1:14">
@@ -19336,7 +19339,7 @@
         <v>646</v>
       </c>
       <c r="E296" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="F296">
         <v>1</v>
@@ -19354,16 +19357,16 @@
         <v>0</v>
       </c>
       <c r="K296" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L296" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M296" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="N296" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="297" spans="1:14">
@@ -19398,16 +19401,16 @@
         <v>0</v>
       </c>
       <c r="K297" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L297" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M297" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N297" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="298" spans="1:14">
@@ -19424,7 +19427,7 @@
         <v>648</v>
       </c>
       <c r="E298" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F298">
         <v>1</v>
@@ -19442,16 +19445,16 @@
         <v>0</v>
       </c>
       <c r="K298" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L298" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M298" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N298" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="299" spans="1:14">
@@ -19486,16 +19489,16 @@
         <v>0</v>
       </c>
       <c r="K299" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L299" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M299" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="N299" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="300" spans="1:14">
@@ -19530,16 +19533,16 @@
         <v>0</v>
       </c>
       <c r="K300" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L300" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M300" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="N300" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="301" spans="1:14">
@@ -19556,7 +19559,7 @@
         <v>651</v>
       </c>
       <c r="E301" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F301">
         <v>1</v>
@@ -19574,16 +19577,16 @@
         <v>0</v>
       </c>
       <c r="K301" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L301" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M301" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N301" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="302" spans="1:14">
@@ -19600,7 +19603,7 @@
         <v>652</v>
       </c>
       <c r="E302" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F302">
         <v>1</v>
@@ -19618,16 +19621,16 @@
         <v>0</v>
       </c>
       <c r="K302" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L302" s="1" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="M302" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="N302" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="303" spans="1:14">
@@ -19662,16 +19665,16 @@
         <v>0</v>
       </c>
       <c r="K303" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M303" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N303" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="304" spans="1:14">
@@ -19688,7 +19691,7 @@
         <v>654</v>
       </c>
       <c r="E304" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="F304">
         <v>1</v>
@@ -19706,16 +19709,16 @@
         <v>0</v>
       </c>
       <c r="K304" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M304" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="N304" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="305" spans="1:14">
@@ -19732,7 +19735,7 @@
         <v>655</v>
       </c>
       <c r="E305" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="F305">
         <v>1</v>
@@ -19750,16 +19753,16 @@
         <v>0</v>
       </c>
       <c r="K305" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L305" s="1" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M305" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N305" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="306" spans="1:14">
@@ -19794,16 +19797,16 @@
         <v>0</v>
       </c>
       <c r="K306" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L306" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M306" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="N306" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="307" spans="1:14">
@@ -19820,7 +19823,7 @@
         <v>657</v>
       </c>
       <c r="E307" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F307">
         <v>1</v>
@@ -19838,16 +19841,16 @@
         <v>0</v>
       </c>
       <c r="K307" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L307" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M307" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="N307" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="308" spans="1:14">
@@ -19864,7 +19867,7 @@
         <v>658</v>
       </c>
       <c r="E308" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F308">
         <v>1</v>
@@ -19882,16 +19885,16 @@
         <v>0</v>
       </c>
       <c r="K308" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L308" s="1" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M308" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="N308" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="309" spans="1:14">
@@ -19926,16 +19929,16 @@
         <v>0</v>
       </c>
       <c r="K309" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L309" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M309" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N309" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="310" spans="1:14">
@@ -19970,16 +19973,16 @@
         <v>0</v>
       </c>
       <c r="K310" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L310" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M310" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="N310" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="311" spans="1:14">
@@ -19996,7 +19999,7 @@
         <v>661</v>
       </c>
       <c r="E311" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F311">
         <v>1</v>
@@ -20014,16 +20017,16 @@
         <v>0</v>
       </c>
       <c r="K311" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L311" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M311" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="N311" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="312" spans="1:14">
@@ -20058,16 +20061,16 @@
         <v>0</v>
       </c>
       <c r="K312" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L312" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M312" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="N312" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="313" spans="1:14">
@@ -20102,16 +20105,16 @@
         <v>0</v>
       </c>
       <c r="K313" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L313" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M313" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="N313" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="314" spans="1:14">
@@ -20128,7 +20131,7 @@
         <v>664</v>
       </c>
       <c r="E314" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F314">
         <v>1</v>
@@ -20146,16 +20149,16 @@
         <v>0</v>
       </c>
       <c r="K314" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L314" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M314" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N314" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="315" spans="1:14">
@@ -20172,7 +20175,7 @@
         <v>665</v>
       </c>
       <c r="E315" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F315">
         <v>1</v>
@@ -20190,16 +20193,16 @@
         <v>0</v>
       </c>
       <c r="K315" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L315" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M315" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="N315" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="316" spans="1:14">
@@ -20234,16 +20237,16 @@
         <v>0</v>
       </c>
       <c r="K316" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L316" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M316" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="N316" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="317" spans="1:14">
@@ -20278,16 +20281,16 @@
         <v>0</v>
       </c>
       <c r="K317" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L317" s="1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="M317" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="N317" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="318" spans="1:14">
@@ -20304,7 +20307,7 @@
         <v>668</v>
       </c>
       <c r="E318" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F318">
         <v>1</v>
@@ -20322,16 +20325,16 @@
         <v>0</v>
       </c>
       <c r="K318" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L318" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M318" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="N318" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="319" spans="1:14">
@@ -20348,7 +20351,7 @@
         <v>669</v>
       </c>
       <c r="E319" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F319">
         <v>1</v>
@@ -20366,16 +20369,16 @@
         <v>0</v>
       </c>
       <c r="K319" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L319" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M319" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="N319" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="320" spans="1:14">
@@ -20410,16 +20413,16 @@
         <v>0</v>
       </c>
       <c r="K320" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L320" s="1" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M320" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="N320" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="321" spans="1:14">
@@ -20454,16 +20457,16 @@
         <v>0</v>
       </c>
       <c r="K321" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L321" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M321" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="N321" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="322" spans="1:14">
@@ -20480,7 +20483,7 @@
         <v>672</v>
       </c>
       <c r="E322" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F322">
         <v>1</v>
@@ -20498,16 +20501,16 @@
         <v>0</v>
       </c>
       <c r="K322" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L322" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M322" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="N322" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="323" spans="1:14">
@@ -20524,7 +20527,7 @@
         <v>673</v>
       </c>
       <c r="E323" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F323">
         <v>1</v>
@@ -20542,16 +20545,16 @@
         <v>0</v>
       </c>
       <c r="K323" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L323" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M323" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="N323" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="324" spans="1:14">
@@ -20586,16 +20589,16 @@
         <v>0</v>
       </c>
       <c r="K324" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L324" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="M324" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="N324" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="325" spans="1:14">
@@ -20630,16 +20633,16 @@
         <v>0</v>
       </c>
       <c r="K325" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L325" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M325" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="N325" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="326" spans="1:14">
@@ -20656,7 +20659,7 @@
         <v>676</v>
       </c>
       <c r="E326" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F326">
         <v>1</v>
@@ -20674,16 +20677,16 @@
         <v>0</v>
       </c>
       <c r="K326" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L326" s="1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M326" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N326" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="327" spans="1:14">
@@ -20700,7 +20703,7 @@
         <v>677</v>
       </c>
       <c r="E327" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F327">
         <v>1</v>
@@ -20718,16 +20721,16 @@
         <v>0</v>
       </c>
       <c r="K327" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L327" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M327" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="N327" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="328" spans="1:14">
@@ -20762,16 +20765,16 @@
         <v>0</v>
       </c>
       <c r="K328" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L328" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M328" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="N328" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="329" spans="1:14">
@@ -20788,7 +20791,7 @@
         <v>679</v>
       </c>
       <c r="E329" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="F329">
         <v>1</v>
@@ -20806,16 +20809,16 @@
         <v>0</v>
       </c>
       <c r="K329" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L329" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M329" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="N329" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="330" spans="1:14">
@@ -20832,7 +20835,7 @@
         <v>680</v>
       </c>
       <c r="E330" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F330">
         <v>1</v>
@@ -20850,16 +20853,16 @@
         <v>0</v>
       </c>
       <c r="K330" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L330" s="1" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="M330" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="N330" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="331" spans="1:14">
@@ -20894,16 +20897,16 @@
         <v>0</v>
       </c>
       <c r="K331" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M331" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="N331" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="332" spans="1:14">
@@ -20938,16 +20941,16 @@
         <v>0</v>
       </c>
       <c r="K332" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="M332" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N332" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="333" spans="1:14">
@@ -20964,7 +20967,7 @@
         <v>682</v>
       </c>
       <c r="E333" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="F333">
         <v>1</v>
@@ -20982,16 +20985,16 @@
         <v>0</v>
       </c>
       <c r="K333" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L333" s="1" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="M333" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="N333" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="334" spans="1:14">
@@ -21026,16 +21029,16 @@
         <v>0</v>
       </c>
       <c r="K334" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L334" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="M334" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N334" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="335" spans="1:14">
@@ -21070,16 +21073,16 @@
         <v>0</v>
       </c>
       <c r="K335" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="M335" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="N335" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="336" spans="1:14">
@@ -21096,7 +21099,7 @@
         <v>685</v>
       </c>
       <c r="E336" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F336">
         <v>1</v>
@@ -21114,16 +21117,16 @@
         <v>0</v>
       </c>
       <c r="K336" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="M336" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="N336" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="337" spans="1:14">
@@ -21140,7 +21143,7 @@
         <v>686</v>
       </c>
       <c r="E337" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F337">
         <v>1</v>
@@ -21158,16 +21161,16 @@
         <v>0</v>
       </c>
       <c r="K337" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="M337" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="N337" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="338" spans="1:14">
@@ -21184,7 +21187,7 @@
         <v>687</v>
       </c>
       <c r="E338" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F338">
         <v>1</v>
@@ -21202,16 +21205,16 @@
         <v>0</v>
       </c>
       <c r="K338" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="M338" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="N338" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="339" spans="1:14">
@@ -21228,7 +21231,7 @@
         <v>688</v>
       </c>
       <c r="E339" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F339">
         <v>1</v>
@@ -21246,16 +21249,16 @@
         <v>0</v>
       </c>
       <c r="K339" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L339" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="M339" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="N339" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="340" spans="1:14">
@@ -21272,7 +21275,7 @@
         <v>689</v>
       </c>
       <c r="E340" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F340">
         <v>1</v>
@@ -21290,16 +21293,16 @@
         <v>0</v>
       </c>
       <c r="K340" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L340" s="1" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="M340" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="N340" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="341" spans="1:14">
@@ -21316,7 +21319,7 @@
         <v>690</v>
       </c>
       <c r="E341" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F341">
         <v>1</v>
@@ -21334,16 +21337,16 @@
         <v>0</v>
       </c>
       <c r="K341" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L341" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="M341" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="N341" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="342" spans="1:14">
@@ -21360,7 +21363,7 @@
         <v>691</v>
       </c>
       <c r="E342" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F342">
         <v>7</v>
@@ -21378,16 +21381,16 @@
         <v>0</v>
       </c>
       <c r="K342" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L342" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M342" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="N342" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="343" spans="1:14">
@@ -21419,16 +21422,16 @@
         <v>0</v>
       </c>
       <c r="K343" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="L343" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="M343" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="N343" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="344" spans="1:14">
@@ -21445,7 +21448,7 @@
         <v>693</v>
       </c>
       <c r="E344" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F344">
         <v>1</v>
@@ -21463,16 +21466,16 @@
         <v>0</v>
       </c>
       <c r="K344" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="L344" s="1" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="M344" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="N344" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="345" spans="1:14">
@@ -21507,16 +21510,16 @@
         <v>0</v>
       </c>
       <c r="K345" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="L345" s="1" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="M345" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="N345" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
   </sheetData>

--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -10415,7 +10415,7 @@
         <v>3</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K91" t="s">
         <v>853</v>
@@ -10717,7 +10717,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="s">
         <v>853</v>

--- a/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
+++ b/research/catalogue-engine/out/consolidated/verification_worklist.xlsx
@@ -372,7 +372,7 @@
     <t>627 &amp; Experiment 627 &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Angel &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Jumba Jookiba &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Kixx &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Leroy &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Reuben &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Richter &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Sinker &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Splodyhead &amp; Stitch – Experiment 626 mystery pin set (626 Day 2026) | Stitch &amp; Yaarp – Experiment 626 mystery pin set (626 Day 2026)</t>
   </si>
   <si>
-    <t>Baymax – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Fozzie Bear – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Genie – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Hercules – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Lucky – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Mad Hatter – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Marie – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Powerline – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Stitch – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack | Winnie the Pooh – UK: Valentine's Day Limited Release Mystery Pin Set | AU: Disney Valentine's Day 2026 Mystery 2-Piece Pin Blind Pack</t>
+    <t>Baymax – Valentine's Day Limited Release Mystery Pin Set | Fozzie Bear – Valentine's Day Limited Release Mystery Pin Set | Genie – Valentine's Day Limited Release Mystery Pin Set | Hercules – Valentine's Day Limited Release Mystery Pin Set | Lucky – Valentine's Day Limited Release Mystery Pin Set | Mad Hatter – Valentine's Day Limited Release Mystery Pin Set | Marie – Valentine's Day Limited Release Mystery Pin Set | Powerline – Valentine's Day Limited Release Mystery Pin Set | Stitch – Valentine's Day Limited Release Mystery Pin Set | Winnie the Pooh – Valentine's Day Limited Release Mystery Pin Set</t>
   </si>
   <si>
     <t>Daisy Duck - Mickey's Christmas Carol Advent Calendar Pin | Donald Duck – Mickey's Christmas Carol 24-Day Advent Calendar Mystery Pin Set 2024 | Goofy - Mickey's Christmas Carol Advent Calendar Pin | Jiminy Cricket as The Ghost of Christmas Past | Mickey Mouse – Mickey's Christmas Carol 24-Day Advent Calendar Mystery Pin Set 2024 | Minnie Mouse - Mickey's Christmas Carol Advent Calendar Pin | Scrooge McDuck – Mickey's Christmas Carol 24-Day Advent Calendar Mystery Pin Set 2024</t>
